--- a/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
+++ b/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-switchbox\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC39CA73-7E57-49C8-81EA-1F188D062E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58068066-FCA1-43E7-B2B4-69A27234D82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="222">
   <si>
     <t>Component list</t>
   </si>
@@ -487,9 +487,6 @@
     <t>STMicroelectronics</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>LCSC Part Number</t>
   </si>
   <si>
@@ -547,9 +544,6 @@
     <t>C105578</t>
   </si>
   <si>
-    <t>C106232</t>
-  </si>
-  <si>
     <t>C2910695</t>
   </si>
   <si>
@@ -565,9 +559,6 @@
     <t>C435835</t>
   </si>
   <si>
-    <t>C908113</t>
-  </si>
-  <si>
     <t>22uF</t>
   </si>
   <si>
@@ -677,6 +668,24 @@
   </si>
   <si>
     <t>C96446</t>
+  </si>
+  <si>
+    <t>C105873</t>
+  </si>
+  <si>
+    <t>RC0402JR-075K1L</t>
+  </si>
+  <si>
+    <t>C60491</t>
+  </si>
+  <si>
+    <t>C2935235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixic </t>
+  </si>
+  <si>
+    <t>C181730</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1332,6 +1341,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1729,7 +1741,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1754,7 +1766,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1779,7 +1791,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1907,37 +1919,37 @@
         <v>135</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="K9" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="M9" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="R9" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="K9" s="67" t="s">
+      <c r="S9" s="30" t="s">
         <v>197</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="M9" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="P9" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="R9" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1965,13 +1977,13 @@
         <v>136</v>
       </c>
       <c r="I10" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L10" s="52">
         <v>2</v>
@@ -1984,7 +1996,7 @@
         <v>40</v>
       </c>
       <c r="O10" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P10" s="50">
         <v>2.3900000000000001E-2</v>
@@ -2021,13 +2033,13 @@
         <v>137</v>
       </c>
       <c r="I11" s="48" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J11" s="48" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K11" s="48" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L11" s="48">
         <v>3</v>
@@ -2040,7 +2052,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P11" s="51">
         <v>8.0000000000000004E-4</v>
@@ -2077,13 +2089,13 @@
         <v>138</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J12" s="45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K12" s="45" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L12" s="45">
         <v>1</v>
@@ -2096,7 +2108,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P12" s="50">
         <v>4.5999999999999999E-3</v>
@@ -2133,13 +2145,13 @@
         <v>137</v>
       </c>
       <c r="I13" s="48" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J13" s="48" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K13" s="48" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L13" s="48">
         <v>1</v>
@@ -2152,7 +2164,7 @@
         <v>20</v>
       </c>
       <c r="O13" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P13" s="51">
         <v>2.3400000000000001E-2</v>
@@ -2189,13 +2201,13 @@
         <v>138</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J14" s="45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L14" s="45">
         <v>1</v>
@@ -2208,7 +2220,7 @@
         <v>50</v>
       </c>
       <c r="O14" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P14" s="50">
         <v>1.5599999999999999E-2</v>
@@ -2239,19 +2251,19 @@
         <v>87</v>
       </c>
       <c r="G15" s="49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H15" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J15" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L15" s="48">
         <v>2</v>
@@ -2261,23 +2273,23 @@
         <v>20</v>
       </c>
       <c r="N15" s="49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q15" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="R15" s="49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="S15" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2305,13 +2317,13 @@
         <v>138</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L16" s="45">
         <v>1</v>
@@ -2324,7 +2336,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P16" s="50">
         <v>2E-3</v>
@@ -2361,13 +2373,13 @@
         <v>138</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J17" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K17" s="48" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L17" s="48">
         <v>1</v>
@@ -2380,7 +2392,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P17" s="51">
         <v>1.3899999999999999E-2</v>
@@ -2399,7 +2411,7 @@
         <v>9</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D18" s="45" t="s">
         <v>28</v>
@@ -2417,13 +2429,13 @@
         <v>139</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J18" s="45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L18" s="45">
         <v>1</v>
@@ -2436,7 +2448,7 @@
         <v>15</v>
       </c>
       <c r="O18" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P18" s="50">
         <v>6.54E-2</v>
@@ -2473,13 +2485,13 @@
         <v>140</v>
       </c>
       <c r="I19" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J19" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K19" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L19" s="48">
         <v>1</v>
@@ -2492,7 +2504,7 @@
         <v>15</v>
       </c>
       <c r="O19" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P19" s="51">
         <v>7.1599999999999997E-2</v>
@@ -2511,7 +2523,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>30</v>
@@ -2520,7 +2532,7 @@
         <v>63</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G20" s="45" t="s">
         <v>92</v>
@@ -2529,7 +2541,7 @@
       <c r="I20" s="45"/>
       <c r="J20" s="45"/>
       <c r="K20" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L20" s="45">
         <v>1</v>
@@ -2555,7 +2567,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="70" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D21" s="48" t="s">
         <v>31</v>
@@ -2564,7 +2576,7 @@
         <v>64</v>
       </c>
       <c r="F21" s="48" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>119</v>
@@ -2573,13 +2585,13 @@
         <v>141</v>
       </c>
       <c r="I21" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J21" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K21" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L21" s="48">
         <v>1</v>
@@ -2592,7 +2604,7 @@
         <v>15</v>
       </c>
       <c r="O21" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P21" s="51">
         <v>0.2276</v>
@@ -2620,7 +2632,7 @@
         <v>65</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G22" s="46" t="s">
         <v>93</v>
@@ -2629,13 +2641,13 @@
         <v>142</v>
       </c>
       <c r="I22" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J22" s="45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L22" s="45">
         <v>1</v>
@@ -2648,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="O22" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P22" s="50">
         <v>0.129</v>
@@ -2676,7 +2688,7 @@
         <v>66</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G23" s="49" t="s">
         <v>94</v>
@@ -2685,13 +2697,13 @@
         <v>143</v>
       </c>
       <c r="I23" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J23" s="48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K23" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L23" s="48">
         <v>10</v>
@@ -2704,7 +2716,7 @@
         <v>105</v>
       </c>
       <c r="O23" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P23" s="51">
         <v>0.25779999999999997</v>
@@ -2741,13 +2753,13 @@
         <v>144</v>
       </c>
       <c r="I24" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J24" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K24" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L24" s="45">
         <v>10</v>
@@ -2760,7 +2772,7 @@
         <v>110</v>
       </c>
       <c r="O24" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P24" s="50">
         <v>6.7900000000000002E-2</v>
@@ -2788,7 +2800,7 @@
         <v>68</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G25" s="49" t="s">
         <v>96</v>
@@ -2798,10 +2810,10 @@
       </c>
       <c r="I25" s="48"/>
       <c r="J25" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K25" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L25" s="48">
         <v>11</v>
@@ -2814,7 +2826,7 @@
         <v>120</v>
       </c>
       <c r="O25" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P25" s="51">
         <v>9.9199999999999997E-2</v>
@@ -2833,7 +2845,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="69" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D26" s="45" t="s">
         <v>36</v>
@@ -2842,22 +2854,22 @@
         <v>69</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G26" s="45" t="s">
         <v>97</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L26" s="45">
         <v>4</v>
@@ -2867,16 +2879,16 @@
         <v>40</v>
       </c>
       <c r="N26" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O26" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P26" s="50" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q26" s="50" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="R26" s="46"/>
       <c r="S26" s="50"/>
@@ -2888,7 +2900,7 @@
         <v>18</v>
       </c>
       <c r="C27" s="70" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D27" s="48" t="s">
         <v>37</v>
@@ -2906,13 +2918,13 @@
         <v>145</v>
       </c>
       <c r="I27" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J27" s="48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K27" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L27" s="48">
         <v>1</v>
@@ -2925,7 +2937,7 @@
         <v>15</v>
       </c>
       <c r="O27" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P27" s="51">
         <v>6.7400000000000002E-2</v>
@@ -2944,7 +2956,7 @@
         <v>19</v>
       </c>
       <c r="C28" s="69" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D28" s="45" t="s">
         <v>38</v>
@@ -2962,13 +2974,13 @@
         <v>146</v>
       </c>
       <c r="I28" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J28" s="45" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K28" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L28" s="45">
         <v>1</v>
@@ -2981,7 +2993,7 @@
         <v>50</v>
       </c>
       <c r="O28" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P28" s="50">
         <v>1.47E-2</v>
@@ -3019,10 +3031,10 @@
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K29" s="48" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L29" s="48">
         <v>6</v>
@@ -3066,13 +3078,13 @@
         <v>148</v>
       </c>
       <c r="I30" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J30" s="45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K30" s="45" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L30" s="45">
         <v>3</v>
@@ -3085,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="71" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P30" s="50">
         <v>6.4000000000000003E-3</v>
@@ -3122,13 +3134,13 @@
         <v>149</v>
       </c>
       <c r="I31" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J31" s="48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K31" s="48" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L31" s="48">
         <v>3</v>
@@ -3141,7 +3153,7 @@
         <v>50</v>
       </c>
       <c r="O31" s="73" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P31" s="51">
         <v>7.7999999999999996E-3</v>
@@ -3171,16 +3183,20 @@
       <c r="F32" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="G32" s="46" t="s">
+      <c r="G32" s="74" t="s">
         <v>126</v>
       </c>
       <c r="H32" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
+      <c r="I32" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="J32" s="45" t="s">
+        <v>216</v>
+      </c>
       <c r="K32" s="45" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L32" s="45">
         <v>2</v>
@@ -3189,12 +3205,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="50"/>
+      <c r="N32" s="45">
+        <v>100</v>
+      </c>
+      <c r="O32" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="P32" s="50">
+        <v>5.0000000000000001E-4</v>
+      </c>
       <c r="Q32" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R32" s="46"/>
       <c r="S32" s="50"/>
@@ -3223,12 +3245,14 @@
       <c r="H33" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="I33" s="48"/>
+      <c r="I33" s="48" t="s">
+        <v>202</v>
+      </c>
       <c r="J33" s="48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K33" s="48" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L33" s="48">
         <v>1</v>
@@ -3237,12 +3261,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="51"/>
+      <c r="N33" s="48">
+        <v>100</v>
+      </c>
+      <c r="O33" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="P33" s="51">
+        <v>1.4E-3</v>
+      </c>
       <c r="Q33" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R33" s="49"/>
       <c r="S33" s="51"/>
@@ -3271,10 +3301,14 @@
       <c r="H34" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
+      <c r="I34" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="J34" s="45" t="s">
+        <v>218</v>
+      </c>
       <c r="K34" s="45" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L34" s="45">
         <v>1</v>
@@ -3283,12 +3317,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="50"/>
+      <c r="N34" s="45">
+        <v>100</v>
+      </c>
+      <c r="O34" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="P34" s="50">
+        <v>5.0000000000000001E-4</v>
+      </c>
       <c r="Q34" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R34" s="46"/>
       <c r="S34" s="50"/>
@@ -3317,12 +3357,14 @@
       <c r="H35" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="I35" s="48"/>
+      <c r="I35" s="48" t="s">
+        <v>202</v>
+      </c>
       <c r="J35" s="48" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L35" s="48">
         <v>10</v>
@@ -3331,12 +3373,18 @@
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="51"/>
+      <c r="N35" s="48">
+        <v>200</v>
+      </c>
+      <c r="O35" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="P35" s="51">
+        <v>6.9999999999999999E-4</v>
+      </c>
       <c r="Q35" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R35" s="49"/>
       <c r="S35" s="51"/>
@@ -3357,7 +3405,7 @@
         <v>79</v>
       </c>
       <c r="F36" s="45" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G36" s="46" t="s">
         <v>103</v>
@@ -3365,12 +3413,14 @@
       <c r="H36" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="I36" s="45"/>
+      <c r="I36" s="45" t="s">
+        <v>202</v>
+      </c>
       <c r="J36" s="45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K36" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L36" s="45">
         <v>1</v>
@@ -3379,12 +3429,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="50"/>
+      <c r="N36" s="45">
+        <v>20</v>
+      </c>
+      <c r="O36" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="P36" s="50">
+        <v>1.7999999999999999E-2</v>
+      </c>
       <c r="Q36" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="R36" s="46"/>
       <c r="S36" s="50"/>
@@ -3413,12 +3469,14 @@
       <c r="H37" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="I37" s="48"/>
+      <c r="I37" s="48" t="s">
+        <v>202</v>
+      </c>
       <c r="J37" s="48" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L37" s="48">
         <v>1</v>
@@ -3427,12 +3485,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="51"/>
+      <c r="N37" s="48">
+        <v>11</v>
+      </c>
+      <c r="O37" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="P37" s="51">
+        <v>3.3553000000000002</v>
+      </c>
       <c r="Q37" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>36.908300000000004</v>
       </c>
       <c r="R37" s="49"/>
       <c r="S37" s="51"/>
@@ -3461,12 +3525,14 @@
       <c r="H38" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="I38" s="45"/>
+      <c r="I38" s="45" t="s">
+        <v>202</v>
+      </c>
       <c r="J38" s="45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K38" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L38" s="45">
         <v>1</v>
@@ -3475,12 +3541,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="50"/>
+      <c r="N38" s="45">
+        <v>11</v>
+      </c>
+      <c r="O38" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="P38" s="50">
+        <v>0.70960000000000001</v>
+      </c>
       <c r="Q38" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.8056000000000001</v>
       </c>
       <c r="R38" s="46"/>
       <c r="S38" s="50"/>
@@ -3509,12 +3581,14 @@
       <c r="H39" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="I39" s="48"/>
+      <c r="I39" s="48" t="s">
+        <v>202</v>
+      </c>
       <c r="J39" s="48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L39" s="48">
         <v>10</v>
@@ -3523,12 +3597,18 @@
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N39" s="48"/>
-      <c r="O39" s="48"/>
-      <c r="P39" s="51"/>
+      <c r="N39" s="48">
+        <v>105</v>
+      </c>
+      <c r="O39" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="P39" s="51">
+        <v>0.11749999999999999</v>
+      </c>
       <c r="Q39" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.337499999999999</v>
       </c>
       <c r="R39" s="49"/>
       <c r="S39" s="51"/>
@@ -3557,12 +3637,14 @@
       <c r="H40" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="I40" s="45"/>
+      <c r="I40" s="45" t="s">
+        <v>202</v>
+      </c>
       <c r="J40" s="45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K40" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L40" s="45">
         <v>1</v>
@@ -3571,12 +3653,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N40" s="45"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="50"/>
+      <c r="N40" s="45">
+        <v>15</v>
+      </c>
+      <c r="O40" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="P40" s="50">
+        <v>0.3513</v>
+      </c>
       <c r="Q40" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.2694999999999999</v>
       </c>
       <c r="R40" s="46"/>
       <c r="S40" s="50"/>
@@ -3603,14 +3691,16 @@
         <v>134</v>
       </c>
       <c r="H41" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="I41" s="48"/>
+        <v>220</v>
+      </c>
+      <c r="I41" s="48" t="s">
+        <v>202</v>
+      </c>
       <c r="J41" s="48" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L41" s="48">
         <v>2</v>
@@ -3619,12 +3709,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N41" s="48"/>
-      <c r="O41" s="48"/>
-      <c r="P41" s="51"/>
+      <c r="N41" s="48">
+        <v>25</v>
+      </c>
+      <c r="O41" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="P41" s="51">
+        <v>8.1199999999999994E-2</v>
+      </c>
       <c r="Q41" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="R41" s="49"/>
       <c r="S41" s="51"/>
@@ -3696,9 +3792,19 @@
     <hyperlink ref="O28" r:id="rId16" xr:uid="{C6504500-546C-423F-893B-28D6DA42E4F7}"/>
     <hyperlink ref="O30" r:id="rId17" xr:uid="{ADA5B89D-EF9A-427B-86ED-25ECFD2C1BEB}"/>
     <hyperlink ref="O31" r:id="rId18" xr:uid="{C8130DAA-34AE-4E20-9121-7EC1F059B813}"/>
+    <hyperlink ref="O32" r:id="rId19" xr:uid="{0760B43C-F473-4C7B-9BB2-B4785A54B864}"/>
+    <hyperlink ref="O33" r:id="rId20" xr:uid="{80365478-7D4F-4298-B8A0-5B830250FF7F}"/>
+    <hyperlink ref="O34" r:id="rId21" xr:uid="{2F15CACC-E877-400C-AF8C-6D941C0E9E1A}"/>
+    <hyperlink ref="O35" r:id="rId22" xr:uid="{177304F5-C295-47FB-961B-5E3A1E1C4732}"/>
+    <hyperlink ref="O36" r:id="rId23" xr:uid="{6F70ADEF-E864-4D13-91BC-C9E9488F0F32}"/>
+    <hyperlink ref="O37" r:id="rId24" xr:uid="{58C7DEB9-7ECA-44CE-9BFE-5A219FC559C1}"/>
+    <hyperlink ref="O38" r:id="rId25" xr:uid="{C7EE6E03-4AEB-4816-8A0A-BB0E31CFBA87}"/>
+    <hyperlink ref="O39" r:id="rId26" xr:uid="{EAA21C97-CD09-4516-AB51-2716850C59BA}"/>
+    <hyperlink ref="O40" r:id="rId27" xr:uid="{950C4C9C-339D-4300-B792-F7567D466B6D}"/>
+    <hyperlink ref="O41" r:id="rId28" xr:uid="{0F21039F-6B3C-4119-AC4F-06AA73524D9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
-  <drawing r:id="rId20"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
+  <drawing r:id="rId30"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
+++ b/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-switchbox\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58068066-FCA1-43E7-B2B4-69A27234D82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1D597B-EDFD-4C71-AA51-8F5EDE2FD466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1140,7 +1140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1298,6 +1298,30 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1322,28 +1346,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1722,15 +1728,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="60"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1780,7 +1786,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="61"/>
+      <c r="S3" s="69"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1805,7 +1811,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="62"/>
+      <c r="S4" s="70"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1830,7 +1836,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="62"/>
+      <c r="S5" s="70"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1851,7 +1857,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="62"/>
+      <c r="S6" s="70"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1872,7 +1878,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="62"/>
+      <c r="S7" s="70"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1893,7 +1899,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="62"/>
+      <c r="S8" s="70"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1924,13 +1930,13 @@
       <c r="J9" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="K9" s="67" t="s">
+      <c r="K9" s="59" t="s">
         <v>194</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="60" t="s">
         <v>198</v>
       </c>
       <c r="N9" s="31" t="s">
@@ -1958,10 +1964,10 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="75" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="46" t="s">
@@ -1995,7 +2001,7 @@
       <c r="N10" s="45">
         <v>40</v>
       </c>
-      <c r="O10" s="71" t="s">
+      <c r="O10" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P10" s="50">
@@ -2014,10 +2020,10 @@
         <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="76" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="49" t="s">
@@ -2026,7 +2032,7 @@
       <c r="F11" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="64" t="s">
         <v>111</v>
       </c>
       <c r="H11" s="48" t="s">
@@ -2051,7 +2057,7 @@
       <c r="N11" s="48">
         <v>100</v>
       </c>
-      <c r="O11" s="73" t="s">
+      <c r="O11" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P11" s="51">
@@ -2070,10 +2076,10 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="75" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="46" t="s">
@@ -2107,7 +2113,7 @@
       <c r="N12" s="45">
         <v>100</v>
       </c>
-      <c r="O12" s="71" t="s">
+      <c r="O12" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P12" s="50">
@@ -2126,10 +2132,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="76" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="49" t="s">
@@ -2138,7 +2144,7 @@
       <c r="F13" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="64" t="s">
         <v>113</v>
       </c>
       <c r="H13" s="48" t="s">
@@ -2163,7 +2169,7 @@
       <c r="N13" s="48">
         <v>20</v>
       </c>
-      <c r="O13" s="73" t="s">
+      <c r="O13" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P13" s="51">
@@ -2182,10 +2188,10 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="75" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="46" t="s">
@@ -2219,7 +2225,7 @@
       <c r="N14" s="45">
         <v>50</v>
       </c>
-      <c r="O14" s="71" t="s">
+      <c r="O14" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P14" s="50">
@@ -2238,10 +2244,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="76" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="49" t="s">
@@ -2298,10 +2304,10 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="75" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="46" t="s">
@@ -2335,7 +2341,7 @@
       <c r="N16" s="45">
         <v>100</v>
       </c>
-      <c r="O16" s="71" t="s">
+      <c r="O16" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P16" s="50">
@@ -2354,10 +2360,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D17" s="76" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="49" t="s">
@@ -2391,7 +2397,7 @@
       <c r="N17" s="48">
         <v>50</v>
       </c>
-      <c r="O17" s="73" t="s">
+      <c r="O17" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P17" s="51">
@@ -2410,10 +2416,10 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="75" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="46" t="s">
@@ -2447,7 +2453,7 @@
       <c r="N18" s="45">
         <v>15</v>
       </c>
-      <c r="O18" s="71" t="s">
+      <c r="O18" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P18" s="50">
@@ -2466,10 +2472,10 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="76" t="s">
         <v>29</v>
       </c>
       <c r="E19" s="49" t="s">
@@ -2503,7 +2509,7 @@
       <c r="N19" s="48">
         <v>15</v>
       </c>
-      <c r="O19" s="73" t="s">
+      <c r="O19" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P19" s="51">
@@ -2522,10 +2528,10 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="61" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="75" t="s">
         <v>30</v>
       </c>
       <c r="E20" s="46" t="s">
@@ -2566,10 +2572,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="76" t="s">
         <v>31</v>
       </c>
       <c r="E21" s="49" t="s">
@@ -2603,7 +2609,7 @@
       <c r="N21" s="48">
         <v>15</v>
       </c>
-      <c r="O21" s="73" t="s">
+      <c r="O21" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P21" s="51">
@@ -2622,10 +2628,10 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="75" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="46" t="s">
@@ -2659,7 +2665,7 @@
       <c r="N22" s="45">
         <v>12</v>
       </c>
-      <c r="O22" s="71" t="s">
+      <c r="O22" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P22" s="50">
@@ -2678,10 +2684,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="76" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="49" t="s">
@@ -2715,7 +2721,7 @@
       <c r="N23" s="48">
         <v>105</v>
       </c>
-      <c r="O23" s="73" t="s">
+      <c r="O23" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P23" s="51">
@@ -2734,10 +2740,10 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="75" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="46" t="s">
@@ -2771,7 +2777,7 @@
       <c r="N24" s="45">
         <v>110</v>
       </c>
-      <c r="O24" s="71" t="s">
+      <c r="O24" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P24" s="50">
@@ -2790,10 +2796,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="70" t="s">
+      <c r="C25" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="76" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="49" t="s">
@@ -2825,7 +2831,7 @@
       <c r="N25" s="48">
         <v>120</v>
       </c>
-      <c r="O25" s="73" t="s">
+      <c r="O25" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P25" s="51">
@@ -2844,10 +2850,10 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="61" t="s">
         <v>210</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" s="75" t="s">
         <v>36</v>
       </c>
       <c r="E26" s="46" t="s">
@@ -2899,10 +2905,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="70" t="s">
+      <c r="C27" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="76" t="s">
         <v>37</v>
       </c>
       <c r="E27" s="49" t="s">
@@ -2936,7 +2942,7 @@
       <c r="N27" s="48">
         <v>15</v>
       </c>
-      <c r="O27" s="73" t="s">
+      <c r="O27" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P27" s="51">
@@ -2955,10 +2961,10 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="75" t="s">
         <v>38</v>
       </c>
       <c r="E28" s="46" t="s">
@@ -2992,7 +2998,7 @@
       <c r="N28" s="45">
         <v>50</v>
       </c>
-      <c r="O28" s="71" t="s">
+      <c r="O28" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P28" s="50">
@@ -3011,10 +3017,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="70" t="s">
+      <c r="C29" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="76" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="49" t="s">
@@ -3059,10 +3065,10 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="75" t="s">
         <v>40</v>
       </c>
       <c r="E30" s="46" t="s">
@@ -3096,7 +3102,7 @@
       <c r="N30" s="45">
         <v>100</v>
       </c>
-      <c r="O30" s="71" t="s">
+      <c r="O30" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P30" s="50">
@@ -3115,10 +3121,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="76" t="s">
         <v>41</v>
       </c>
       <c r="E31" s="49" t="s">
@@ -3152,7 +3158,7 @@
       <c r="N31" s="48">
         <v>50</v>
       </c>
-      <c r="O31" s="73" t="s">
+      <c r="O31" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P31" s="51">
@@ -3171,10 +3177,10 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="45" t="s">
+      <c r="D32" s="75" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="46" t="s">
@@ -3183,7 +3189,7 @@
       <c r="F32" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="G32" s="74" t="s">
+      <c r="G32" s="66" t="s">
         <v>126</v>
       </c>
       <c r="H32" s="45" t="s">
@@ -3208,7 +3214,7 @@
       <c r="N32" s="45">
         <v>100</v>
       </c>
-      <c r="O32" s="71" t="s">
+      <c r="O32" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P32" s="50">
@@ -3227,10 +3233,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="70" t="s">
+      <c r="C33" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="76" t="s">
         <v>43</v>
       </c>
       <c r="E33" s="49" t="s">
@@ -3264,7 +3270,7 @@
       <c r="N33" s="48">
         <v>100</v>
       </c>
-      <c r="O33" s="73" t="s">
+      <c r="O33" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P33" s="51">
@@ -3283,10 +3289,10 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="75" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="46" t="s">
@@ -3320,7 +3326,7 @@
       <c r="N34" s="45">
         <v>100</v>
       </c>
-      <c r="O34" s="71" t="s">
+      <c r="O34" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P34" s="50">
@@ -3339,10 +3345,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="76" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="49" t="s">
@@ -3376,7 +3382,7 @@
       <c r="N35" s="48">
         <v>200</v>
       </c>
-      <c r="O35" s="73" t="s">
+      <c r="O35" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P35" s="51">
@@ -3395,10 +3401,10 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="45" t="s">
+      <c r="D36" s="75" t="s">
         <v>46</v>
       </c>
       <c r="E36" s="46" t="s">
@@ -3432,7 +3438,7 @@
       <c r="N36" s="45">
         <v>20</v>
       </c>
-      <c r="O36" s="71" t="s">
+      <c r="O36" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P36" s="50">
@@ -3451,10 +3457,10 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="70" t="s">
+      <c r="C37" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" s="76" t="s">
         <v>47</v>
       </c>
       <c r="E37" s="49" t="s">
@@ -3488,7 +3494,7 @@
       <c r="N37" s="48">
         <v>11</v>
       </c>
-      <c r="O37" s="73" t="s">
+      <c r="O37" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P37" s="51">
@@ -3507,10 +3513,10 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="69" t="s">
+      <c r="C38" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" s="75" t="s">
         <v>48</v>
       </c>
       <c r="E38" s="46" t="s">
@@ -3544,7 +3550,7 @@
       <c r="N38" s="45">
         <v>11</v>
       </c>
-      <c r="O38" s="71" t="s">
+      <c r="O38" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P38" s="50">
@@ -3563,10 +3569,10 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="70" t="s">
+      <c r="C39" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="76" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="49" t="s">
@@ -3600,7 +3606,7 @@
       <c r="N39" s="48">
         <v>105</v>
       </c>
-      <c r="O39" s="73" t="s">
+      <c r="O39" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P39" s="51">
@@ -3619,10 +3625,10 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="45" t="s">
+      <c r="D40" s="75" t="s">
         <v>50</v>
       </c>
       <c r="E40" s="46" t="s">
@@ -3656,7 +3662,7 @@
       <c r="N40" s="45">
         <v>15</v>
       </c>
-      <c r="O40" s="71" t="s">
+      <c r="O40" s="63" t="s">
         <v>211</v>
       </c>
       <c r="P40" s="50">
@@ -3675,10 +3681,10 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="70" t="s">
+      <c r="C41" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="76" t="s">
         <v>51</v>
       </c>
       <c r="E41" s="49" t="s">
@@ -3712,7 +3718,7 @@
       <c r="N41" s="48">
         <v>25</v>
       </c>
-      <c r="O41" s="73" t="s">
+      <c r="O41" s="65" t="s">
         <v>211</v>
       </c>
       <c r="P41" s="51">
@@ -3743,8 +3749,8 @@
       <c r="O42" s="36"/>
       <c r="P42" s="36"/>
       <c r="Q42" s="36"/>
-      <c r="R42" s="63"/>
-      <c r="S42" s="64"/>
+      <c r="R42" s="71"/>
+      <c r="S42" s="72"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -3764,8 +3770,8 @@
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="66"/>
+      <c r="R43" s="73"/>
+      <c r="S43" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
+++ b/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-switchbox\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1D597B-EDFD-4C71-AA51-8F5EDE2FD466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DF0CD8-013A-46E4-82FA-425161595944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="233">
   <si>
     <t>Component list</t>
   </si>
@@ -127,9 +127,6 @@
     <t>LED1, LED2, LED3, LED4, LED5, LED6, LED7, LED8, LED9, LED10</t>
   </si>
   <si>
-    <t>P1, P4, P5, P6, P7, P8, P9, P10, P11, P12, P13</t>
-  </si>
-  <si>
     <t>P2, P3, P14, P15</t>
   </si>
   <si>
@@ -211,24 +208,15 @@
     <t>6V 1A 50A 1W -40℃~+85℃ 2A 9mΩ 0.5s 80mΩ 0603 Resettable Fuses ROHS</t>
   </si>
   <si>
-    <t>DNP</t>
-  </si>
-  <si>
     <t>250mA 1 16 Female Type-C SMD USB Connectors ROHS</t>
   </si>
   <si>
-    <t>Plugin,P=5mm Screw terminal ROHS</t>
-  </si>
-  <si>
     <t>AgCdO 5V 10A SPDT (1 Form C) Electromagnetic Relay-Single Coil Plugin Power Relays ROHS</t>
   </si>
   <si>
     <t>Green 520~535nm 0402 Light Emitting Diodes (LED) RoHS</t>
   </si>
   <si>
-    <t>P=5.0mm Screw terminal RoHS</t>
-  </si>
-  <si>
     <t>Test Point ON</t>
   </si>
   <si>
@@ -238,9 +226,6 @@
     <t>Trans Gp Bjt NPN 25V 1.5A 300MW 3-PIN SOT-23 T/r</t>
   </si>
   <si>
-    <t>RES SMD 10K OHM 5% 1/5W 0603, RES SMD 10K Ohm 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>4 8 ±5% 330Ω 62.5mW ±250ppm/℃ 0402x4 Resistor Networks &amp; Arrays ROHS</t>
   </si>
   <si>
@@ -298,21 +283,12 @@
     <t>fuse-0603</t>
   </si>
   <si>
-    <t>Voltlink Target</t>
-  </si>
-  <si>
-    <t>WJ301V-5.0-4P-12-00A</t>
-  </si>
-  <si>
     <t>JQC-3FF/005-1ZS(551)</t>
   </si>
   <si>
     <t>LED-0402</t>
   </si>
   <si>
-    <t>WJ301V-5.0-3P</t>
-  </si>
-  <si>
     <t>Test-point</t>
   </si>
   <si>
@@ -391,9 +367,6 @@
     <t>SS8050-G</t>
   </si>
   <si>
-    <t>CRGH0603J10K, RC0603FR-0710KL</t>
-  </si>
-  <si>
     <t>CN24JTN331</t>
   </si>
   <si>
@@ -463,9 +436,6 @@
     <t>Comchip</t>
   </si>
   <si>
-    <t>TE Connectivity Holsworthy, Yageo</t>
-  </si>
-  <si>
     <t>TA-I Tech</t>
   </si>
   <si>
@@ -514,27 +484,18 @@
     <t>C165948</t>
   </si>
   <si>
-    <t>C3031442</t>
-  </si>
-  <si>
     <t>C9221</t>
   </si>
   <si>
     <t>C74338</t>
   </si>
   <si>
-    <t>C8483</t>
-  </si>
-  <si>
     <t>C725031</t>
   </si>
   <si>
     <t>C105433</t>
   </si>
   <si>
-    <t>C2092011, C98220</t>
-  </si>
-  <si>
     <t>C162973</t>
   </si>
   <si>
@@ -686,17 +647,91 @@
   </si>
   <si>
     <t>C181730</t>
+  </si>
+  <si>
+    <t>C21, C22</t>
+  </si>
+  <si>
+    <t>-45℃~+105℃ 2000hrs@105℃ 47uF 5.4mm 16V 5mm ±20% SMD,D5xL5.4mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
+  </si>
+  <si>
+    <t>RVT1C470M0505</t>
+  </si>
+  <si>
+    <t>ROQANG</t>
+  </si>
+  <si>
+    <t>C72515</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
+  </si>
+  <si>
+    <t>C145963</t>
+  </si>
+  <si>
+    <t>BOOMELE</t>
+  </si>
+  <si>
+    <t>450V 17.5A 4 Bend -40℃~+105℃ 1 5.08mm Green Board Edge/Receptacle-Open Push-Pull,P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>DB2ER-5.08-4P-GN</t>
+  </si>
+  <si>
+    <t>DIBO</t>
+  </si>
+  <si>
+    <t>C395752</t>
+  </si>
+  <si>
+    <t>J4, J5, J6, J7, J8, J9, J10, J11, J12, J13, J14</t>
+  </si>
+  <si>
+    <t>3 Bend 1 5.08mm Green Board Edge/Receptacle-Open Push-Pull,P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>WJ2EDGR-5.08-3P</t>
+  </si>
+  <si>
+    <t>C70914</t>
+  </si>
+  <si>
+    <t>SMD,D5xL5.4mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Component Cost </t>
+  </si>
+  <si>
+    <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>RES 10K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-0710KL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+YAGEO</t>
+  </si>
+  <si>
+    <t>C98220</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,6 +892,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -890,7 +932,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1135,12 +1177,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1319,9 +1374,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1352,6 +1404,43 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1694,7 +1783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1710,7 +1799,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -1728,15 +1817,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="68"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1747,7 +1836,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1772,7 +1861,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1786,7 +1875,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="69"/>
+      <c r="S3" s="68"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1797,7 +1886,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1811,7 +1900,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="70"/>
+      <c r="S4" s="69"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1836,7 +1925,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="70"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1857,7 +1946,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="70"/>
+      <c r="S6" s="69"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1878,7 +1967,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="70"/>
+      <c r="S7" s="69"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1899,7 +1988,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="70"/>
+      <c r="S8" s="69"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1913,49 +2002,49 @@
         <v>19</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="K9" s="59" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M9" s="60" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1967,29 +2056,29 @@
       <c r="C10" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="I10" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="L10" s="52">
         <v>2</v>
@@ -2002,7 +2091,7 @@
         <v>40</v>
       </c>
       <c r="O10" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P10" s="50">
         <v>2.3900000000000001E-2</v>
@@ -2017,54 +2106,54 @@
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="37">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="75" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G11" s="64" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H11" s="48" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I11" s="48" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J11" s="48" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="K11" s="48" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="L11" s="48">
         <v>3</v>
       </c>
       <c r="M11" s="48">
-        <f t="shared" ref="M11:M41" si="1">L11*10</f>
+        <f t="shared" ref="M11:M42" si="1">L11*10</f>
         <v>30</v>
       </c>
       <c r="N11" s="48">
         <v>100</v>
       </c>
       <c r="O11" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P11" s="51">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q11" s="51">
-        <f t="shared" ref="Q11:Q41" si="2">P11*N11</f>
+        <f t="shared" ref="Q11:Q42" si="2">P11*N11</f>
         <v>0.08</v>
       </c>
       <c r="R11" s="49"/>
@@ -2079,29 +2168,29 @@
       <c r="C12" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="74" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H12" s="45" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J12" s="45" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="K12" s="45" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="L12" s="45">
         <v>1</v>
@@ -2114,7 +2203,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P12" s="50">
         <v>4.5999999999999999E-3</v>
@@ -2135,29 +2224,29 @@
       <c r="C13" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="75" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="48" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G13" s="64" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H13" s="48" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I13" s="48" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="J13" s="48" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="K13" s="48" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="L13" s="48">
         <v>1</v>
@@ -2170,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="O13" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P13" s="51">
         <v>2.3400000000000001E-2</v>
@@ -2191,29 +2280,29 @@
       <c r="C14" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="74" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H14" s="45" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J14" s="45" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="L14" s="45">
         <v>1</v>
@@ -2226,7 +2315,7 @@
         <v>50</v>
       </c>
       <c r="O14" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P14" s="50">
         <v>1.5599999999999999E-2</v>
@@ -2247,29 +2336,29 @@
       <c r="C15" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="75" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G15" s="49" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H15" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J15" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L15" s="48">
         <v>2</v>
@@ -2279,23 +2368,22 @@
         <v>20</v>
       </c>
       <c r="N15" s="49" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q15" s="51" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>189</v>
+      </c>
+      <c r="Q15" s="51" t="s">
+        <v>189</v>
       </c>
       <c r="R15" s="49" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="S15" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2307,29 +2395,29 @@
       <c r="C16" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="74" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G16" s="46" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H16" s="45" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="L16" s="45">
         <v>1</v>
@@ -2342,7 +2430,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P16" s="50">
         <v>2E-3</v>
@@ -2363,29 +2451,29 @@
       <c r="C17" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="75" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H17" s="48" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J17" s="48" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="K17" s="48" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="L17" s="48">
         <v>1</v>
@@ -2398,7 +2486,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P17" s="51">
         <v>1.3899999999999999E-2</v>
@@ -2410,58 +2498,58 @@
       <c r="R17" s="49"/>
       <c r="S17" s="51"/>
     </row>
-    <row r="18" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="37">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="75" t="s">
-        <v>28</v>
+        <v>7</v>
+      </c>
+      <c r="D18" s="74" t="s">
+        <v>209</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="F18" s="45" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="G18" s="46" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="H18" s="45" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J18" s="45" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="L18" s="45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="45">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N18" s="45">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="O18" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P18" s="50">
-        <v>6.54E-2</v>
+        <v>2.75E-2</v>
       </c>
       <c r="Q18" s="50">
-        <f t="shared" si="2"/>
-        <v>0.98099999999999998</v>
+        <f>P18*N18</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R18" s="46"/>
       <c r="S18" s="50"/>
@@ -2469,35 +2557,35 @@
     <row r="19" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
       <c r="C19" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>29</v>
+        <v>193</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>28</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="48" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H19" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="48" t="s">
-        <v>202</v>
+        <v>130</v>
+      </c>
+      <c r="I19" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J19" s="48" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="K19" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L19" s="48">
         <v>1</v>
@@ -2510,44 +2598,50 @@
         <v>15</v>
       </c>
       <c r="O19" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P19" s="51">
-        <v>7.1599999999999997E-2</v>
+        <v>6.54E-2</v>
       </c>
       <c r="Q19" s="51">
         <f t="shared" si="2"/>
-        <v>1.0739999999999998</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="R19" s="49"/>
       <c r="S19" s="51"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="37">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>207</v>
-      </c>
-      <c r="D20" s="75" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>29</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+        <v>86</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="45" t="s">
+        <v>152</v>
+      </c>
       <c r="K20" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L20" s="45">
         <v>1</v>
@@ -2556,12 +2650,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="50"/>
+      <c r="N20" s="45">
+        <v>15</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P20" s="50">
+        <v>7.1599999999999997E-2</v>
+      </c>
       <c r="Q20" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0739999999999998</v>
       </c>
       <c r="R20" s="46"/>
       <c r="S20" s="50"/>
@@ -2569,35 +2669,35 @@
     <row r="21" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
       <c r="C21" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="D21" s="76" t="s">
-        <v>31</v>
+        <v>194</v>
+      </c>
+      <c r="D21" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>64</v>
+        <v>215</v>
       </c>
       <c r="F21" s="48" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="H21" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="I21" s="48" t="s">
-        <v>202</v>
+        <v>217</v>
+      </c>
+      <c r="I21" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J21" s="48" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="K21" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L21" s="48">
         <v>1</v>
@@ -2607,53 +2707,53 @@
         <v>10</v>
       </c>
       <c r="N21" s="48">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O21" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P21" s="51">
-        <v>0.2276</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="Q21" s="51">
         <f t="shared" si="2"/>
-        <v>3.4140000000000001</v>
+        <v>0.86399999999999988</v>
       </c>
       <c r="R21" s="49"/>
       <c r="S21" s="51"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="37">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="75" t="s">
-        <v>32</v>
+        <v>195</v>
+      </c>
+      <c r="D22" s="74" t="s">
+        <v>31</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H22" s="45" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I22" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J22" s="45" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L22" s="45">
         <v>1</v>
@@ -2663,294 +2763,296 @@
         <v>10</v>
       </c>
       <c r="N22" s="45">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O22" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P22" s="50">
-        <v>0.129</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" s="50">
         <f t="shared" si="2"/>
-        <v>1.548</v>
+        <v>3.4140000000000001</v>
       </c>
       <c r="R22" s="46"/>
       <c r="S22" s="50"/>
     </row>
-    <row r="23" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="76" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>32</v>
       </c>
       <c r="E23" s="49" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G23" s="49" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="H23" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="48" t="s">
-        <v>202</v>
+        <v>220</v>
+      </c>
+      <c r="I23" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J23" s="48" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="K23" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L23" s="48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M23" s="48">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="N23" s="48">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="O23" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P23" s="51">
-        <v>0.25779999999999997</v>
+        <v>6.5600000000000006E-2</v>
       </c>
       <c r="Q23" s="51">
         <f t="shared" si="2"/>
-        <v>27.068999999999996</v>
+        <v>0.9840000000000001</v>
       </c>
       <c r="R23" s="49"/>
       <c r="S23" s="51"/>
     </row>
-    <row r="24" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="37">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
       <c r="C24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="K24" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L24" s="45">
         <v>11</v>
-      </c>
-      <c r="D24" s="75" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="I24" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="J24" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="K24" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="L24" s="45">
-        <v>10</v>
       </c>
       <c r="M24" s="45">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N24" s="45">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O24" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P24" s="50">
-        <v>6.7900000000000002E-2</v>
+        <v>4.6100000000000002E-2</v>
       </c>
       <c r="Q24" s="50">
-        <f t="shared" si="2"/>
-        <v>7.4690000000000003</v>
+        <f>P24*N24</f>
+        <v>5.532</v>
       </c>
       <c r="R24" s="46"/>
       <c r="S24" s="50"/>
     </row>
-    <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="76" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>33</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H25" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I25" s="48"/>
+        <v>134</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>189</v>
+      </c>
       <c r="J25" s="48" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="K25" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L25" s="48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M25" s="48">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="N25" s="48">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="O25" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P25" s="51">
-        <v>9.9199999999999997E-2</v>
+        <v>0.25779999999999997</v>
       </c>
       <c r="Q25" s="51">
         <f t="shared" si="2"/>
-        <v>11.904</v>
+        <v>27.068999999999996</v>
       </c>
       <c r="R25" s="49"/>
       <c r="S25" s="51"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="37">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="D26" s="74" t="s">
+        <v>34</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="G26" s="45" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>112</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L26" s="45">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M26" s="45">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N26" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="O26" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="P26" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q26" s="50" t="s">
-        <v>202</v>
+        <v>100</v>
+      </c>
+      <c r="N26" s="45">
+        <v>110</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P26" s="50">
+        <v>6.7900000000000002E-2</v>
+      </c>
+      <c r="Q26" s="50">
+        <f t="shared" si="2"/>
+        <v>7.4690000000000003</v>
       </c>
       <c r="R26" s="46"/>
       <c r="S26" s="50"/>
     </row>
-    <row r="27" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>37</v>
+        <v>197</v>
+      </c>
+      <c r="D27" s="75" t="s">
+        <v>35</v>
       </c>
       <c r="E27" s="49" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="G27" s="49" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="H27" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="I27" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J27" s="48" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="K27" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L27" s="48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M27" s="48">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N27" s="48">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="N27" s="48" t="s">
+        <v>189</v>
       </c>
       <c r="O27" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="P27" s="51">
-        <v>6.7400000000000002E-2</v>
-      </c>
-      <c r="Q27" s="51">
-        <f t="shared" si="2"/>
-        <v>1.0110000000000001</v>
+        <v>189</v>
+      </c>
+      <c r="P27" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q27" s="51" t="s">
+        <v>189</v>
       </c>
       <c r="R27" s="49"/>
       <c r="S27" s="51"/>
@@ -2958,35 +3060,35 @@
     <row r="28" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="37">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="D28" s="75" t="s">
-        <v>38</v>
+        <v>196</v>
+      </c>
+      <c r="D28" s="74" t="s">
+        <v>36</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G28" s="46" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H28" s="45" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I28" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J28" s="45" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="K28" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L28" s="45">
         <v>1</v>
@@ -2996,17 +3098,17 @@
         <v>10</v>
       </c>
       <c r="N28" s="45">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P28" s="50">
-        <v>1.47E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="Q28" s="50">
         <f t="shared" si="2"/>
-        <v>0.73499999999999999</v>
+        <v>1.0110000000000001</v>
       </c>
       <c r="R28" s="46"/>
       <c r="S28" s="50"/>
@@ -3014,139 +3116,147 @@
     <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>39</v>
+        <v>196</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>37</v>
       </c>
       <c r="E29" s="49" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G29" s="49" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H29" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="I29" s="48"/>
+        <v>137</v>
+      </c>
+      <c r="I29" s="49" t="s">
+        <v>189</v>
+      </c>
       <c r="J29" s="48" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="K29" s="48" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L29" s="48">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M29" s="48">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="51"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="48">
+        <v>50</v>
+      </c>
+      <c r="O29" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" s="51">
+        <v>1.47E-2</v>
+      </c>
       <c r="Q29" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="R29" s="49"/>
       <c r="S29" s="51"/>
     </row>
-    <row r="30" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="37">
-        <f>ROW(B30) - ROW($B$9)</f>
+    <row r="30" spans="1:19" s="88" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="80"/>
+      <c r="B30" s="81">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="45" t="s">
+      <c r="C30" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="84" t="s">
+        <v>229</v>
+      </c>
+      <c r="F30" s="85" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="H30" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="I30" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="85" t="s">
+        <v>232</v>
+      </c>
+      <c r="K30" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="L30" s="85">
+        <v>6</v>
+      </c>
+      <c r="M30" s="85">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="N30" s="85">
         <v>100</v>
       </c>
-      <c r="G30" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H30" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="J30" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="K30" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="L30" s="45">
-        <v>3</v>
-      </c>
-      <c r="M30" s="45">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N30" s="45">
-        <v>100</v>
-      </c>
-      <c r="O30" s="63" t="s">
-        <v>211</v>
-      </c>
-      <c r="P30" s="50">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="Q30" s="50">
+      <c r="O30" s="86" t="s">
+        <v>198</v>
+      </c>
+      <c r="P30" s="87">
+        <v>1E-3</v>
+      </c>
+      <c r="Q30" s="87">
         <f t="shared" si="2"/>
-        <v>0.64</v>
-      </c>
-      <c r="R30" s="46"/>
-      <c r="S30" s="50"/>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30" s="87"/>
+    </row>
+    <row r="31" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>41</v>
+        <v>12</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>39</v>
       </c>
       <c r="E31" s="49" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F31" s="48" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="H31" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="I31" s="48" t="s">
-        <v>202</v>
+        <v>138</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J31" s="48" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="K31" s="48" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="L31" s="48">
         <v>3</v>
@@ -3156,17 +3266,17 @@
         <v>30</v>
       </c>
       <c r="N31" s="48">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O31" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P31" s="51">
-        <v>7.7999999999999996E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="Q31" s="51">
         <f t="shared" si="2"/>
-        <v>0.38999999999999996</v>
+        <v>0.64</v>
       </c>
       <c r="R31" s="49"/>
       <c r="S31" s="51"/>
@@ -3174,55 +3284,55 @@
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="37">
-        <f>ROW(B32) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="75" t="s">
-        <v>42</v>
+      <c r="D32" s="74" t="s">
+        <v>40</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="66" t="s">
-        <v>126</v>
+        <v>93</v>
+      </c>
+      <c r="G32" s="46" t="s">
+        <v>116</v>
       </c>
       <c r="H32" s="45" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I32" s="45" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="J32" s="45" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="K32" s="45" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L32" s="45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="45">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N32" s="45">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O32" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P32" s="50">
-        <v>5.0000000000000001E-4</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="Q32" s="50">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.38999999999999996</v>
       </c>
       <c r="R32" s="46"/>
       <c r="S32" s="50"/>
@@ -3230,55 +3340,55 @@
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="76" t="s">
-        <v>43</v>
+      <c r="D33" s="75" t="s">
+        <v>41</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F33" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="49" t="s">
-        <v>127</v>
+        <v>93</v>
+      </c>
+      <c r="G33" s="64" t="s">
+        <v>117</v>
       </c>
       <c r="H33" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="I33" s="48" t="s">
-        <v>202</v>
+        <v>139</v>
+      </c>
+      <c r="I33" s="49" t="s">
+        <v>204</v>
       </c>
       <c r="J33" s="48" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="K33" s="48" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L33" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="48">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N33" s="48">
         <v>100</v>
       </c>
       <c r="O33" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P33" s="51">
-        <v>1.4E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q33" s="51">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="R33" s="49"/>
       <c r="S33" s="51"/>
@@ -3286,35 +3396,35 @@
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="37">
-        <f>ROW(B34) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="75" t="s">
-        <v>44</v>
+      <c r="D34" s="74" t="s">
+        <v>42</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F34" s="45" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G34" s="46" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H34" s="45" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I34" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J34" s="45" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="K34" s="45" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="L34" s="45">
         <v>1</v>
@@ -3327,162 +3437,162 @@
         <v>100</v>
       </c>
       <c r="O34" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P34" s="50">
-        <v>5.0000000000000001E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q34" s="50">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R34" s="46"/>
       <c r="S34" s="50"/>
     </row>
-    <row r="35" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="76" t="s">
-        <v>45</v>
+      <c r="D35" s="75" t="s">
+        <v>43</v>
       </c>
       <c r="E35" s="49" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F35" s="48" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G35" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="H35" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="I35" s="48" t="s">
-        <v>202</v>
+      <c r="I35" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J35" s="48" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="L35" s="48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M35" s="48">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N35" s="48">
         <v>100</v>
       </c>
-      <c r="N35" s="48">
-        <v>200</v>
-      </c>
       <c r="O35" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P35" s="51">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q35" s="51">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="R35" s="49"/>
       <c r="S35" s="51"/>
     </row>
-    <row r="36" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="37">
-        <f>ROW(B36) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="75" t="s">
-        <v>46</v>
+        <v>13</v>
+      </c>
+      <c r="D36" s="74" t="s">
+        <v>44</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F36" s="45" t="s">
-        <v>203</v>
+        <v>93</v>
       </c>
       <c r="G36" s="46" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="H36" s="45" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I36" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J36" s="45" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="K36" s="45" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="L36" s="45">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M36" s="45">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N36" s="45">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="O36" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P36" s="50">
-        <v>1.7999999999999999E-2</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q36" s="50">
         <f t="shared" si="2"/>
-        <v>0.36</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R36" s="46"/>
       <c r="S36" s="50"/>
     </row>
-    <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="76" t="s">
-        <v>47</v>
+        <v>14</v>
+      </c>
+      <c r="D37" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F37" s="48" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="H37" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="I37" s="48" t="s">
-        <v>202</v>
+        <v>140</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J37" s="48" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L37" s="48">
         <v>1</v>
@@ -3492,53 +3602,53 @@
         <v>10</v>
       </c>
       <c r="N37" s="48">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O37" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P37" s="51">
-        <v>3.3553000000000002</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="Q37" s="51">
         <f t="shared" si="2"/>
-        <v>36.908300000000004</v>
+        <v>0.36</v>
       </c>
       <c r="R37" s="49"/>
       <c r="S37" s="51"/>
     </row>
-    <row r="38" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="37">
-        <f>ROW(B38) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="75" t="s">
-        <v>48</v>
+        <v>15</v>
+      </c>
+      <c r="D38" s="74" t="s">
+        <v>46</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F38" s="45" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G38" s="46" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H38" s="45" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I38" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J38" s="45" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="K38" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L38" s="45">
         <v>1</v>
@@ -3551,126 +3661,126 @@
         <v>11</v>
       </c>
       <c r="O38" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P38" s="50">
-        <v>0.70960000000000001</v>
+        <v>3.3553000000000002</v>
       </c>
       <c r="Q38" s="50">
         <f t="shared" si="2"/>
-        <v>7.8056000000000001</v>
+        <v>36.908300000000004</v>
       </c>
       <c r="R38" s="46"/>
       <c r="S38" s="50"/>
     </row>
-    <row r="39" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="76" t="s">
-        <v>49</v>
+        <v>16</v>
+      </c>
+      <c r="D39" s="75" t="s">
+        <v>47</v>
       </c>
       <c r="E39" s="49" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F39" s="48" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H39" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="I39" s="48" t="s">
-        <v>202</v>
+        <v>142</v>
+      </c>
+      <c r="I39" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J39" s="48" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L39" s="48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M39" s="48">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="N39" s="48">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="O39" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P39" s="51">
-        <v>0.11749999999999999</v>
+        <v>0.70960000000000001</v>
       </c>
       <c r="Q39" s="51">
         <f t="shared" si="2"/>
-        <v>12.337499999999999</v>
+        <v>7.8056000000000001</v>
       </c>
       <c r="R39" s="49"/>
       <c r="S39" s="51"/>
     </row>
-    <row r="40" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="37">
-        <f>ROW(B40) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="75" t="s">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="D40" s="74" t="s">
+        <v>48</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F40" s="45" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G40" s="46" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H40" s="45" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I40" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J40" s="45" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="K40" s="45" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L40" s="45">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M40" s="45">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N40" s="45">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="O40" s="63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P40" s="50">
-        <v>0.3513</v>
+        <v>0.11749999999999999</v>
       </c>
       <c r="Q40" s="50">
         <f t="shared" si="2"/>
-        <v>5.2694999999999999</v>
+        <v>12.337499999999999</v>
       </c>
       <c r="R40" s="46"/>
       <c r="S40" s="50"/>
@@ -3678,106 +3788,174 @@
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="76" t="s">
-        <v>51</v>
+      <c r="D41" s="75" t="s">
+        <v>49</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F41" s="48" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H41" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="I41" s="48" t="s">
-        <v>202</v>
+        <v>144</v>
+      </c>
+      <c r="I41" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="J41" s="48" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L41" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="48">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N41" s="48">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O41" s="65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P41" s="51">
-        <v>8.1199999999999994E-2</v>
+        <v>0.3513</v>
       </c>
       <c r="Q41" s="51">
         <f t="shared" si="2"/>
-        <v>2.0299999999999998</v>
+        <v>5.2694999999999999</v>
       </c>
       <c r="R41" s="49"/>
       <c r="S41" s="51"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="36"/>
-      <c r="N42" s="36"/>
-      <c r="O42" s="36"/>
-      <c r="P42" s="36"/>
-      <c r="Q42" s="36"/>
-      <c r="R42" s="71"/>
-      <c r="S42" s="72"/>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="37">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="I42" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J42" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="K42" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L42" s="45">
+        <v>2</v>
+      </c>
+      <c r="M42" s="45">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N42" s="45">
+        <v>25</v>
+      </c>
+      <c r="O42" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P42" s="50">
+        <v>8.1199999999999994E-2</v>
+      </c>
+      <c r="Q42" s="50">
+        <f t="shared" si="2"/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="R42" s="46"/>
+      <c r="S42" s="50"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="73"/>
-      <c r="S43" s="74"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="O43" s="77"/>
+      <c r="P43" s="77"/>
+      <c r="Q43" s="78">
+        <f>SUM(Q15:Q42)</f>
+        <v>117.34889999999999</v>
+      </c>
+      <c r="R43" s="70"/>
+      <c r="S43" s="71"/>
+    </row>
+    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="O44" s="77"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="79">
+        <f>Q43/10</f>
+        <v>11.734889999999998</v>
+      </c>
+      <c r="R44" s="72"/>
+      <c r="S44" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="R43:S44"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{B4B92583-AFC5-4C70-B0C5-E1A2E39FC483}"/>
@@ -3786,31 +3964,34 @@
     <hyperlink ref="O13" r:id="rId4" xr:uid="{9C8DE64B-39DC-4FA5-BC82-70A9347B5CB7}"/>
     <hyperlink ref="O14" r:id="rId5" xr:uid="{B57C6DE4-F114-47CC-A4AE-81250E951A85}"/>
     <hyperlink ref="O16" r:id="rId6" xr:uid="{1033A83E-EF73-44FE-BC7E-01798A863B28}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{43FDAEFF-6403-40D1-9C4E-7D1D36A4547B}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{C6D95856-76AF-4CFB-A4FB-A06F479B4719}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{D31CF805-77DA-485C-A79F-60E569C18A2B}"/>
-    <hyperlink ref="O21" r:id="rId10" xr:uid="{2FA3E246-B558-4663-817E-A113191AF2F4}"/>
-    <hyperlink ref="O22" r:id="rId11" xr:uid="{4D562C0B-01BB-4743-BEF4-306E01B88197}"/>
-    <hyperlink ref="O23" r:id="rId12" xr:uid="{805F7ACB-D787-441E-A591-2AE7335E81B1}"/>
-    <hyperlink ref="O24" r:id="rId13" xr:uid="{021899FA-497D-462B-A309-42059B1C785F}"/>
-    <hyperlink ref="O25" r:id="rId14" xr:uid="{0C6F7394-A2F7-47BD-9325-771E8DAB4B45}"/>
-    <hyperlink ref="O27" r:id="rId15" xr:uid="{FEA5DC77-A5A9-4599-B4FE-89EA64A3C261}"/>
-    <hyperlink ref="O28" r:id="rId16" xr:uid="{C6504500-546C-423F-893B-28D6DA42E4F7}"/>
-    <hyperlink ref="O30" r:id="rId17" xr:uid="{ADA5B89D-EF9A-427B-86ED-25ECFD2C1BEB}"/>
-    <hyperlink ref="O31" r:id="rId18" xr:uid="{C8130DAA-34AE-4E20-9121-7EC1F059B813}"/>
-    <hyperlink ref="O32" r:id="rId19" xr:uid="{0760B43C-F473-4C7B-9BB2-B4785A54B864}"/>
-    <hyperlink ref="O33" r:id="rId20" xr:uid="{80365478-7D4F-4298-B8A0-5B830250FF7F}"/>
-    <hyperlink ref="O34" r:id="rId21" xr:uid="{2F15CACC-E877-400C-AF8C-6D941C0E9E1A}"/>
-    <hyperlink ref="O35" r:id="rId22" xr:uid="{177304F5-C295-47FB-961B-5E3A1E1C4732}"/>
-    <hyperlink ref="O36" r:id="rId23" xr:uid="{6F70ADEF-E864-4D13-91BC-C9E9488F0F32}"/>
-    <hyperlink ref="O37" r:id="rId24" xr:uid="{58C7DEB9-7ECA-44CE-9BFE-5A219FC559C1}"/>
-    <hyperlink ref="O38" r:id="rId25" xr:uid="{C7EE6E03-4AEB-4816-8A0A-BB0E31CFBA87}"/>
-    <hyperlink ref="O39" r:id="rId26" xr:uid="{EAA21C97-CD09-4516-AB51-2716850C59BA}"/>
-    <hyperlink ref="O40" r:id="rId27" xr:uid="{950C4C9C-339D-4300-B792-F7567D466B6D}"/>
-    <hyperlink ref="O41" r:id="rId28" xr:uid="{0F21039F-6B3C-4119-AC4F-06AA73524D9A}"/>
+    <hyperlink ref="O20" r:id="rId7" xr:uid="{D31CF805-77DA-485C-A79F-60E569C18A2B}"/>
+    <hyperlink ref="O22" r:id="rId8" xr:uid="{2FA3E246-B558-4663-817E-A113191AF2F4}"/>
+    <hyperlink ref="O26" r:id="rId9" xr:uid="{021899FA-497D-462B-A309-42059B1C785F}"/>
+    <hyperlink ref="O28" r:id="rId10" xr:uid="{FEA5DC77-A5A9-4599-B4FE-89EA64A3C261}"/>
+    <hyperlink ref="O29" r:id="rId11" xr:uid="{C6504500-546C-423F-893B-28D6DA42E4F7}"/>
+    <hyperlink ref="O31" r:id="rId12" xr:uid="{ADA5B89D-EF9A-427B-86ED-25ECFD2C1BEB}"/>
+    <hyperlink ref="O32" r:id="rId13" xr:uid="{C8130DAA-34AE-4E20-9121-7EC1F059B813}"/>
+    <hyperlink ref="O33" r:id="rId14" xr:uid="{0760B43C-F473-4C7B-9BB2-B4785A54B864}"/>
+    <hyperlink ref="O34" r:id="rId15" xr:uid="{80365478-7D4F-4298-B8A0-5B830250FF7F}"/>
+    <hyperlink ref="O35" r:id="rId16" xr:uid="{2F15CACC-E877-400C-AF8C-6D941C0E9E1A}"/>
+    <hyperlink ref="O36" r:id="rId17" xr:uid="{177304F5-C295-47FB-961B-5E3A1E1C4732}"/>
+    <hyperlink ref="O37" r:id="rId18" xr:uid="{6F70ADEF-E864-4D13-91BC-C9E9488F0F32}"/>
+    <hyperlink ref="O38" r:id="rId19" xr:uid="{58C7DEB9-7ECA-44CE-9BFE-5A219FC559C1}"/>
+    <hyperlink ref="O39" r:id="rId20" xr:uid="{C7EE6E03-4AEB-4816-8A0A-BB0E31CFBA87}"/>
+    <hyperlink ref="O40" r:id="rId21" xr:uid="{EAA21C97-CD09-4516-AB51-2716850C59BA}"/>
+    <hyperlink ref="O41" r:id="rId22" xr:uid="{950C4C9C-339D-4300-B792-F7567D466B6D}"/>
+    <hyperlink ref="O42" r:id="rId23" xr:uid="{0F21039F-6B3C-4119-AC4F-06AA73524D9A}"/>
+    <hyperlink ref="O25" r:id="rId24" xr:uid="{805F7ACB-D787-441E-A591-2AE7335E81B1}"/>
+    <hyperlink ref="O19" r:id="rId25" xr:uid="{C6D95856-76AF-4CFB-A4FB-A06F479B4719}"/>
+    <hyperlink ref="O17" r:id="rId26" xr:uid="{43FDAEFF-6403-40D1-9C4E-7D1D36A4547B}"/>
+    <hyperlink ref="O18" r:id="rId27" xr:uid="{139A5CC0-C786-4F85-AA66-3AEE409EB113}"/>
+    <hyperlink ref="O21" r:id="rId28" xr:uid="{8C8DA922-14BF-412F-BFF6-B7E698A6F7FE}"/>
+    <hyperlink ref="O23" r:id="rId29" xr:uid="{8F538101-09B9-4F97-96DB-04960D66F6EE}"/>
+    <hyperlink ref="O24" r:id="rId30" xr:uid="{9A904CE7-14A6-4D9E-9A55-CB2910411196}"/>
+    <hyperlink ref="O30" r:id="rId31" xr:uid="{AA1C896D-0A54-4267-B8EF-A8CBFBFDAF8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
-  <drawing r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
+  <drawing r:id="rId33"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
+++ b/Deliverables/BOM/eSpark_BOM(10 pcs).xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-switchbox\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DF0CD8-013A-46E4-82FA-425161595944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3502CC26-80BE-4B8A-8474-5DDC5AF91975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="1000 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="237">
   <si>
     <t>Component list</t>
   </si>
@@ -617,12 +618,6 @@
   </si>
   <si>
     <t>LCSC</t>
-  </si>
-  <si>
-    <t>CC0402KRX7R9BB103</t>
-  </si>
-  <si>
-    <t>C60133</t>
   </si>
   <si>
     <t>CL10A106MA8NRNC</t>
@@ -720,6 +715,24 @@
   </si>
   <si>
     <t>C98220</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>C131394</t>
+  </si>
+  <si>
+    <t>Quantity (1000 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (1000 Boards)</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1374,6 +1387,51 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1396,12 +1454,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1412,35 +1464,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1508,6 +1531,60 @@
         <a:xfrm>
           <a:off x="29927550" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D684445-58C1-42BB-9964-62CEEA4B8D5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18097500" y="620016"/>
+          <a:ext cx="1714500" cy="1113533"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1817,15 +1894,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="67"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="82"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1875,7 +1952,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="68"/>
+      <c r="S3" s="83"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1900,7 +1977,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="69"/>
+      <c r="S4" s="84"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1925,7 +2002,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="69"/>
+      <c r="S5" s="84"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1946,7 +2023,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="69"/>
+      <c r="S6" s="84"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1967,7 +2044,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="69"/>
+      <c r="S7" s="84"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1988,7 +2065,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="69"/>
+      <c r="S8" s="84"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2056,7 +2133,7 @@
       <c r="C10" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="66" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="46" t="s">
@@ -2112,7 +2189,7 @@
       <c r="C11" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="67" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="49" t="s">
@@ -2128,10 +2205,10 @@
         <v>128</v>
       </c>
       <c r="I11" s="48" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="J11" s="48" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="K11" s="48" t="s">
         <v>167</v>
@@ -2150,11 +2227,11 @@
         <v>198</v>
       </c>
       <c r="P11" s="51">
-        <v>8.0000000000000004E-4</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q11" s="51">
         <f t="shared" ref="Q11:Q42" si="2">P11*N11</f>
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="R11" s="49"/>
       <c r="S11" s="54"/>
@@ -2168,7 +2245,7 @@
       <c r="C12" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="66" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="46" t="s">
@@ -2224,7 +2301,7 @@
       <c r="C13" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="67" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="49" t="s">
@@ -2240,10 +2317,10 @@
         <v>128</v>
       </c>
       <c r="I13" s="48" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J13" s="48" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K13" s="48" t="s">
         <v>169</v>
@@ -2280,7 +2357,7 @@
       <c r="C14" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="74" t="s">
+      <c r="D14" s="66" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="46" t="s">
@@ -2336,7 +2413,7 @@
       <c r="C15" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="67" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="49" t="s">
@@ -2395,7 +2472,7 @@
       <c r="C16" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="66" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="46" t="s">
@@ -2451,7 +2528,7 @@
       <c r="C17" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="67" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="49" t="s">
@@ -2507,29 +2584,29 @@
       <c r="C18" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="74" t="s">
+      <c r="D18" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G18" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="H18" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="F18" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="G18" s="46" t="s">
+      <c r="I18" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="K18" s="45" t="s">
         <v>212</v>
-      </c>
-      <c r="I18" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="J18" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>214</v>
       </c>
       <c r="L18" s="45">
         <v>2</v>
@@ -2563,7 +2640,7 @@
       <c r="C19" s="62" t="s">
         <v>193</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="67" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="49" t="s">
@@ -2619,7 +2696,7 @@
       <c r="C20" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="66" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="46" t="s">
@@ -2675,26 +2752,26 @@
       <c r="C21" s="62" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="67" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F21" s="48" t="s">
         <v>190</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H21" s="48" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I21" s="49" t="s">
         <v>189</v>
       </c>
       <c r="J21" s="48" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K21" s="48" t="s">
         <v>189</v>
@@ -2731,7 +2808,7 @@
       <c r="C22" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="74" t="s">
+      <c r="D22" s="66" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="46" t="s">
@@ -2787,26 +2864,26 @@
       <c r="C23" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="75" t="s">
+      <c r="D23" s="67" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="49" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F23" s="48" t="s">
         <v>190</v>
       </c>
       <c r="G23" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="48" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="J23" s="48" t="s">
-        <v>221</v>
       </c>
       <c r="K23" s="48" t="s">
         <v>189</v>
@@ -2843,17 +2920,17 @@
       <c r="C24" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="74" t="s">
-        <v>222</v>
+      <c r="D24" s="66" t="s">
+        <v>220</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F24" s="45" t="s">
         <v>190</v>
       </c>
       <c r="G24" s="46" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H24" s="45" t="s">
         <v>133</v>
@@ -2862,7 +2939,7 @@
         <v>189</v>
       </c>
       <c r="J24" s="45" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K24" s="45" t="s">
         <v>189</v>
@@ -2899,7 +2976,7 @@
       <c r="C25" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="67" t="s">
         <v>33</v>
       </c>
       <c r="E25" s="49" t="s">
@@ -2955,7 +3032,7 @@
       <c r="C26" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="74" t="s">
+      <c r="D26" s="66" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="46" t="s">
@@ -3011,7 +3088,7 @@
       <c r="C27" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="67" t="s">
         <v>35</v>
       </c>
       <c r="E27" s="49" t="s">
@@ -3066,7 +3143,7 @@
       <c r="C28" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="D28" s="74" t="s">
+      <c r="D28" s="66" t="s">
         <v>36</v>
       </c>
       <c r="E28" s="46" t="s">
@@ -3122,7 +3199,7 @@
       <c r="C29" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="67" t="s">
         <v>37</v>
       </c>
       <c r="E29" s="49" t="s">
@@ -3169,61 +3246,61 @@
       <c r="R29" s="49"/>
       <c r="S29" s="51"/>
     </row>
-    <row r="30" spans="1:19" s="88" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="80"/>
-      <c r="B30" s="81">
+    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="70">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="82" t="s">
+      <c r="C30" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="83" t="s">
+      <c r="D30" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="84" t="s">
+      <c r="E30" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="73" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="74" t="s">
         <v>229</v>
       </c>
-      <c r="F30" s="85" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="84" t="s">
+      <c r="I30" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="74" t="s">
         <v>230</v>
       </c>
-      <c r="H30" s="85" t="s">
-        <v>231</v>
-      </c>
-      <c r="I30" s="85" t="s">
-        <v>189</v>
-      </c>
-      <c r="J30" s="85" t="s">
-        <v>232</v>
-      </c>
-      <c r="K30" s="85" t="s">
+      <c r="K30" s="74" t="s">
         <v>172</v>
       </c>
-      <c r="L30" s="85">
+      <c r="L30" s="74">
         <v>6</v>
       </c>
-      <c r="M30" s="85">
+      <c r="M30" s="74">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N30" s="85">
+      <c r="N30" s="74">
         <v>100</v>
       </c>
-      <c r="O30" s="86" t="s">
+      <c r="O30" s="75" t="s">
         <v>198</v>
       </c>
-      <c r="P30" s="87">
+      <c r="P30" s="76">
         <v>1E-3</v>
       </c>
-      <c r="Q30" s="87">
+      <c r="Q30" s="76">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R30" s="84"/>
-      <c r="S30" s="87"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="76"/>
     </row>
     <row r="31" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3234,7 +3311,7 @@
       <c r="C31" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="75" t="s">
+      <c r="D31" s="67" t="s">
         <v>39</v>
       </c>
       <c r="E31" s="49" t="s">
@@ -3290,7 +3367,7 @@
       <c r="C32" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="74" t="s">
+      <c r="D32" s="66" t="s">
         <v>40</v>
       </c>
       <c r="E32" s="46" t="s">
@@ -3346,7 +3423,7 @@
       <c r="C33" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="D33" s="67" t="s">
         <v>41</v>
       </c>
       <c r="E33" s="49" t="s">
@@ -3362,10 +3439,10 @@
         <v>139</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J33" s="48" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K33" s="48" t="s">
         <v>175</v>
@@ -3402,7 +3479,7 @@
       <c r="C34" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="74" t="s">
+      <c r="D34" s="66" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="46" t="s">
@@ -3458,7 +3535,7 @@
       <c r="C35" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="75" t="s">
+      <c r="D35" s="67" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="49" t="s">
@@ -3477,7 +3554,7 @@
         <v>189</v>
       </c>
       <c r="J35" s="48" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K35" s="48" t="s">
         <v>177</v>
@@ -3514,7 +3591,7 @@
       <c r="C36" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="74" t="s">
+      <c r="D36" s="66" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="46" t="s">
@@ -3533,7 +3610,7 @@
         <v>189</v>
       </c>
       <c r="J36" s="45" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K36" s="45" t="s">
         <v>178</v>
@@ -3570,7 +3647,7 @@
       <c r="C37" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="75" t="s">
+      <c r="D37" s="67" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="49" t="s">
@@ -3626,7 +3703,7 @@
       <c r="C38" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="74" t="s">
+      <c r="D38" s="66" t="s">
         <v>46</v>
       </c>
       <c r="E38" s="46" t="s">
@@ -3682,7 +3759,7 @@
       <c r="C39" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="75" t="s">
+      <c r="D39" s="67" t="s">
         <v>47</v>
       </c>
       <c r="E39" s="49" t="s">
@@ -3738,7 +3815,7 @@
       <c r="C40" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="74" t="s">
+      <c r="D40" s="66" t="s">
         <v>48</v>
       </c>
       <c r="E40" s="46" t="s">
@@ -3794,7 +3871,7 @@
       <c r="C41" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="75" t="s">
+      <c r="D41" s="67" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="49" t="s">
@@ -3850,7 +3927,7 @@
       <c r="C42" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="74" t="s">
+      <c r="D42" s="66" t="s">
         <v>50</v>
       </c>
       <c r="E42" s="46" t="s">
@@ -3863,13 +3940,13 @@
         <v>125</v>
       </c>
       <c r="H42" s="45" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I42" s="45" t="s">
         <v>189</v>
       </c>
       <c r="J42" s="45" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K42" s="45" t="s">
         <v>189</v>
@@ -3911,17 +3988,17 @@
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
-      <c r="N43" s="76" t="s">
-        <v>227</v>
-      </c>
-      <c r="O43" s="77"/>
-      <c r="P43" s="77"/>
-      <c r="Q43" s="78">
-        <f>SUM(Q15:Q42)</f>
-        <v>117.34889999999999</v>
-      </c>
-      <c r="R43" s="70"/>
-      <c r="S43" s="71"/>
+      <c r="N43" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="O43" s="90"/>
+      <c r="P43" s="90"/>
+      <c r="Q43" s="68">
+        <f>SUM(Q10:Q42)</f>
+        <v>120.31289999999998</v>
+      </c>
+      <c r="R43" s="85"/>
+      <c r="S43" s="86"/>
     </row>
     <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -3937,17 +4014,17 @@
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
-      <c r="N44" s="76" t="s">
-        <v>228</v>
-      </c>
-      <c r="O44" s="77"/>
-      <c r="P44" s="77"/>
-      <c r="Q44" s="79">
+      <c r="N44" s="89" t="s">
+        <v>226</v>
+      </c>
+      <c r="O44" s="90"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="69">
         <f>Q43/10</f>
-        <v>11.734889999999998</v>
-      </c>
-      <c r="R44" s="72"/>
-      <c r="S44" s="73"/>
+        <v>12.031289999999998</v>
+      </c>
+      <c r="R44" s="87"/>
+      <c r="S44" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3959,39 +4036,2252 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{B4B92583-AFC5-4C70-B0C5-E1A2E39FC483}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{44077763-56FC-4A18-B19C-BF7E6FE42CF2}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{02F1C72C-646B-4E69-843C-7B79512658BB}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{9C8DE64B-39DC-4FA5-BC82-70A9347B5CB7}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{B57C6DE4-F114-47CC-A4AE-81250E951A85}"/>
-    <hyperlink ref="O16" r:id="rId6" xr:uid="{1033A83E-EF73-44FE-BC7E-01798A863B28}"/>
-    <hyperlink ref="O20" r:id="rId7" xr:uid="{D31CF805-77DA-485C-A79F-60E569C18A2B}"/>
-    <hyperlink ref="O22" r:id="rId8" xr:uid="{2FA3E246-B558-4663-817E-A113191AF2F4}"/>
-    <hyperlink ref="O26" r:id="rId9" xr:uid="{021899FA-497D-462B-A309-42059B1C785F}"/>
-    <hyperlink ref="O28" r:id="rId10" xr:uid="{FEA5DC77-A5A9-4599-B4FE-89EA64A3C261}"/>
-    <hyperlink ref="O29" r:id="rId11" xr:uid="{C6504500-546C-423F-893B-28D6DA42E4F7}"/>
-    <hyperlink ref="O31" r:id="rId12" xr:uid="{ADA5B89D-EF9A-427B-86ED-25ECFD2C1BEB}"/>
-    <hyperlink ref="O32" r:id="rId13" xr:uid="{C8130DAA-34AE-4E20-9121-7EC1F059B813}"/>
-    <hyperlink ref="O33" r:id="rId14" xr:uid="{0760B43C-F473-4C7B-9BB2-B4785A54B864}"/>
-    <hyperlink ref="O34" r:id="rId15" xr:uid="{80365478-7D4F-4298-B8A0-5B830250FF7F}"/>
-    <hyperlink ref="O35" r:id="rId16" xr:uid="{2F15CACC-E877-400C-AF8C-6D941C0E9E1A}"/>
-    <hyperlink ref="O36" r:id="rId17" xr:uid="{177304F5-C295-47FB-961B-5E3A1E1C4732}"/>
-    <hyperlink ref="O37" r:id="rId18" xr:uid="{6F70ADEF-E864-4D13-91BC-C9E9488F0F32}"/>
-    <hyperlink ref="O38" r:id="rId19" xr:uid="{58C7DEB9-7ECA-44CE-9BFE-5A219FC559C1}"/>
-    <hyperlink ref="O39" r:id="rId20" xr:uid="{C7EE6E03-4AEB-4816-8A0A-BB0E31CFBA87}"/>
-    <hyperlink ref="O40" r:id="rId21" xr:uid="{EAA21C97-CD09-4516-AB51-2716850C59BA}"/>
-    <hyperlink ref="O41" r:id="rId22" xr:uid="{950C4C9C-339D-4300-B792-F7567D466B6D}"/>
-    <hyperlink ref="O42" r:id="rId23" xr:uid="{0F21039F-6B3C-4119-AC4F-06AA73524D9A}"/>
-    <hyperlink ref="O25" r:id="rId24" xr:uid="{805F7ACB-D787-441E-A591-2AE7335E81B1}"/>
-    <hyperlink ref="O19" r:id="rId25" xr:uid="{C6D95856-76AF-4CFB-A4FB-A06F479B4719}"/>
-    <hyperlink ref="O17" r:id="rId26" xr:uid="{43FDAEFF-6403-40D1-9C4E-7D1D36A4547B}"/>
-    <hyperlink ref="O18" r:id="rId27" xr:uid="{139A5CC0-C786-4F85-AA66-3AEE409EB113}"/>
-    <hyperlink ref="O21" r:id="rId28" xr:uid="{8C8DA922-14BF-412F-BFF6-B7E698A6F7FE}"/>
-    <hyperlink ref="O23" r:id="rId29" xr:uid="{8F538101-09B9-4F97-96DB-04960D66F6EE}"/>
-    <hyperlink ref="O24" r:id="rId30" xr:uid="{9A904CE7-14A6-4D9E-9A55-CB2910411196}"/>
-    <hyperlink ref="O30" r:id="rId31" xr:uid="{AA1C896D-0A54-4267-B8EF-A8CBFBFDAF8E}"/>
+    <hyperlink ref="O12" r:id="rId2" xr:uid="{02F1C72C-646B-4E69-843C-7B79512658BB}"/>
+    <hyperlink ref="O13" r:id="rId3" xr:uid="{9C8DE64B-39DC-4FA5-BC82-70A9347B5CB7}"/>
+    <hyperlink ref="O14" r:id="rId4" xr:uid="{B57C6DE4-F114-47CC-A4AE-81250E951A85}"/>
+    <hyperlink ref="O16" r:id="rId5" xr:uid="{1033A83E-EF73-44FE-BC7E-01798A863B28}"/>
+    <hyperlink ref="O20" r:id="rId6" xr:uid="{D31CF805-77DA-485C-A79F-60E569C18A2B}"/>
+    <hyperlink ref="O22" r:id="rId7" xr:uid="{2FA3E246-B558-4663-817E-A113191AF2F4}"/>
+    <hyperlink ref="O26" r:id="rId8" xr:uid="{021899FA-497D-462B-A309-42059B1C785F}"/>
+    <hyperlink ref="O28" r:id="rId9" xr:uid="{FEA5DC77-A5A9-4599-B4FE-89EA64A3C261}"/>
+    <hyperlink ref="O29" r:id="rId10" xr:uid="{C6504500-546C-423F-893B-28D6DA42E4F7}"/>
+    <hyperlink ref="O31" r:id="rId11" xr:uid="{ADA5B89D-EF9A-427B-86ED-25ECFD2C1BEB}"/>
+    <hyperlink ref="O32" r:id="rId12" xr:uid="{C8130DAA-34AE-4E20-9121-7EC1F059B813}"/>
+    <hyperlink ref="O33" r:id="rId13" xr:uid="{0760B43C-F473-4C7B-9BB2-B4785A54B864}"/>
+    <hyperlink ref="O34" r:id="rId14" xr:uid="{80365478-7D4F-4298-B8A0-5B830250FF7F}"/>
+    <hyperlink ref="O35" r:id="rId15" xr:uid="{2F15CACC-E877-400C-AF8C-6D941C0E9E1A}"/>
+    <hyperlink ref="O36" r:id="rId16" xr:uid="{177304F5-C295-47FB-961B-5E3A1E1C4732}"/>
+    <hyperlink ref="O37" r:id="rId17" xr:uid="{6F70ADEF-E864-4D13-91BC-C9E9488F0F32}"/>
+    <hyperlink ref="O38" r:id="rId18" xr:uid="{58C7DEB9-7ECA-44CE-9BFE-5A219FC559C1}"/>
+    <hyperlink ref="O39" r:id="rId19" xr:uid="{C7EE6E03-4AEB-4816-8A0A-BB0E31CFBA87}"/>
+    <hyperlink ref="O40" r:id="rId20" xr:uid="{EAA21C97-CD09-4516-AB51-2716850C59BA}"/>
+    <hyperlink ref="O41" r:id="rId21" xr:uid="{950C4C9C-339D-4300-B792-F7567D466B6D}"/>
+    <hyperlink ref="O42" r:id="rId22" xr:uid="{0F21039F-6B3C-4119-AC4F-06AA73524D9A}"/>
+    <hyperlink ref="O25" r:id="rId23" xr:uid="{805F7ACB-D787-441E-A591-2AE7335E81B1}"/>
+    <hyperlink ref="O19" r:id="rId24" xr:uid="{C6D95856-76AF-4CFB-A4FB-A06F479B4719}"/>
+    <hyperlink ref="O17" r:id="rId25" xr:uid="{43FDAEFF-6403-40D1-9C4E-7D1D36A4547B}"/>
+    <hyperlink ref="O18" r:id="rId26" xr:uid="{139A5CC0-C786-4F85-AA66-3AEE409EB113}"/>
+    <hyperlink ref="O21" r:id="rId27" xr:uid="{8C8DA922-14BF-412F-BFF6-B7E698A6F7FE}"/>
+    <hyperlink ref="O23" r:id="rId28" xr:uid="{8F538101-09B9-4F97-96DB-04960D66F6EE}"/>
+    <hyperlink ref="O24" r:id="rId29" xr:uid="{9A904CE7-14A6-4D9E-9A55-CB2910411196}"/>
+    <hyperlink ref="O30" r:id="rId30" xr:uid="{AA1C896D-0A54-4267-B8EF-A8CBFBFDAF8E}"/>
+    <hyperlink ref="O11" r:id="rId31" xr:uid="{06B3400B-70EE-41D2-9AFA-71E148298236}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
   <drawing r:id="rId33"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0695B8-3988-408E-B7A3-E10795A47168}">
+  <dimension ref="A1:S44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="82"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="83"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="84"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="84"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="84"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="84"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="84"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="77"/>
+      <c r="B10" s="37">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="L10" s="52">
+        <v>2</v>
+      </c>
+      <c r="M10" s="47">
+        <f>L10*1000</f>
+        <v>2000</v>
+      </c>
+      <c r="N10" s="45">
+        <v>2060</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P10" s="50">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="Q10" s="50">
+        <f>P10*N10</f>
+        <v>29.252000000000002</v>
+      </c>
+      <c r="R10" s="46"/>
+      <c r="S10" s="78"/>
+    </row>
+    <row r="11" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="77"/>
+      <c r="B11" s="37">
+        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="J11" s="48" t="s">
+        <v>232</v>
+      </c>
+      <c r="K11" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="48">
+        <v>3</v>
+      </c>
+      <c r="M11" s="48">
+        <f t="shared" ref="M11:M42" si="1">L11*1000</f>
+        <v>3000</v>
+      </c>
+      <c r="N11" s="48">
+        <v>3100</v>
+      </c>
+      <c r="O11" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" s="51">
+        <v>2E-3</v>
+      </c>
+      <c r="Q11" s="51">
+        <f t="shared" ref="Q11:Q42" si="2">P11*N11</f>
+        <v>6.2</v>
+      </c>
+      <c r="R11" s="49"/>
+      <c r="S11" s="80"/>
+    </row>
+    <row r="12" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="77"/>
+      <c r="B12" s="37">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="I12" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J12" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="L12" s="45">
+        <v>1</v>
+      </c>
+      <c r="M12" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N12" s="45">
+        <v>1100</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P12" s="50">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="Q12" s="50">
+        <f t="shared" si="2"/>
+        <v>3.96</v>
+      </c>
+      <c r="R12" s="46"/>
+      <c r="S12" s="50"/>
+    </row>
+    <row r="13" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="77"/>
+      <c r="B13" s="37">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="J13" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="K13" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="L13" s="48">
+        <v>1</v>
+      </c>
+      <c r="M13" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N13" s="48">
+        <v>1060</v>
+      </c>
+      <c r="O13" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P13" s="51">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="Q13" s="51">
+        <f t="shared" si="2"/>
+        <v>24.804000000000002</v>
+      </c>
+      <c r="R13" s="49"/>
+      <c r="S13" s="51"/>
+    </row>
+    <row r="14" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="77"/>
+      <c r="B14" s="37">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="L14" s="45">
+        <v>1</v>
+      </c>
+      <c r="M14" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N14" s="45">
+        <v>1050</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P14" s="50">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="Q14" s="50">
+        <f t="shared" si="2"/>
+        <v>13.334999999999999</v>
+      </c>
+      <c r="R14" s="46"/>
+      <c r="S14" s="50"/>
+    </row>
+    <row r="15" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="77"/>
+      <c r="B15" s="37">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="K15" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L15" s="48">
+        <v>2</v>
+      </c>
+      <c r="M15" s="48">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="N15" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="O15" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="P15" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q15" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="R15" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="S15" s="48" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="77"/>
+      <c r="B16" s="37">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="K16" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="L16" s="45">
+        <v>1</v>
+      </c>
+      <c r="M16" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N16" s="45">
+        <v>1100</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P16" s="50">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q16" s="50">
+        <f t="shared" si="2"/>
+        <v>1.76</v>
+      </c>
+      <c r="R16" s="46"/>
+      <c r="S16" s="50"/>
+    </row>
+    <row r="17" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="77"/>
+      <c r="B17" s="37">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="K17" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" s="48">
+        <v>1</v>
+      </c>
+      <c r="M17" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N17" s="48">
+        <v>1050</v>
+      </c>
+      <c r="O17" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P17" s="51">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="Q17" s="51">
+        <f t="shared" si="2"/>
+        <v>11.864999999999998</v>
+      </c>
+      <c r="R17" s="49"/>
+      <c r="S17" s="51"/>
+    </row>
+    <row r="18" spans="1:19" s="79" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="77"/>
+      <c r="B18" s="37">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I18" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="K18" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="L18" s="45">
+        <v>2</v>
+      </c>
+      <c r="M18" s="45">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="N18" s="45">
+        <v>2060</v>
+      </c>
+      <c r="O18" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P18" s="50">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="Q18" s="50">
+        <f>P18*N18</f>
+        <v>34.814</v>
+      </c>
+      <c r="R18" s="46"/>
+      <c r="S18" s="50"/>
+    </row>
+    <row r="19" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="77"/>
+      <c r="B19" s="37">
+        <f>ROW(B19) - ROW($B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="K19" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19" s="48">
+        <v>1</v>
+      </c>
+      <c r="M19" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N19" s="48">
+        <v>1050</v>
+      </c>
+      <c r="O19" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P19" s="51">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="Q19" s="51">
+        <f t="shared" si="2"/>
+        <v>44.625</v>
+      </c>
+      <c r="R19" s="49"/>
+      <c r="S19" s="51"/>
+    </row>
+    <row r="20" spans="1:19" s="79" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="77"/>
+      <c r="B20" s="37">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="66" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="K20" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" s="45">
+        <v>1</v>
+      </c>
+      <c r="M20" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N20" s="45">
+        <v>1050</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P20" s="50">
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="Q20" s="50">
+        <f t="shared" si="2"/>
+        <v>49.455000000000005</v>
+      </c>
+      <c r="R20" s="46"/>
+      <c r="S20" s="50"/>
+    </row>
+    <row r="21" spans="1:19" s="79" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="77"/>
+      <c r="B21" s="37">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="62" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="K21" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L21" s="48">
+        <v>1</v>
+      </c>
+      <c r="M21" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N21" s="48">
+        <v>1020</v>
+      </c>
+      <c r="O21" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P21" s="51">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="Q21" s="51">
+        <f t="shared" si="2"/>
+        <v>53.958000000000006</v>
+      </c>
+      <c r="R21" s="49"/>
+      <c r="S21" s="51"/>
+    </row>
+    <row r="22" spans="1:19" s="79" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="77"/>
+      <c r="B22" s="37">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="66" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="K22" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L22" s="45">
+        <v>1</v>
+      </c>
+      <c r="M22" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N22" s="45">
+        <v>1050</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P22" s="50">
+        <v>0.1074</v>
+      </c>
+      <c r="Q22" s="50">
+        <f t="shared" si="2"/>
+        <v>112.77</v>
+      </c>
+      <c r="R22" s="46"/>
+      <c r="S22" s="50"/>
+    </row>
+    <row r="23" spans="1:19" s="79" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="77"/>
+      <c r="B23" s="37">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="G23" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="K23" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L23" s="48">
+        <v>1</v>
+      </c>
+      <c r="M23" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N23" s="48">
+        <v>1050</v>
+      </c>
+      <c r="O23" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P23" s="51">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="Q23" s="51">
+        <f t="shared" si="2"/>
+        <v>44.1</v>
+      </c>
+      <c r="R23" s="49"/>
+      <c r="S23" s="51"/>
+    </row>
+    <row r="24" spans="1:19" s="79" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="77"/>
+      <c r="B24" s="37">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="K24" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L24" s="45">
+        <v>11</v>
+      </c>
+      <c r="M24" s="45">
+        <f t="shared" si="1"/>
+        <v>11000</v>
+      </c>
+      <c r="N24" s="45">
+        <v>11100</v>
+      </c>
+      <c r="O24" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P24" s="50">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="Q24" s="50">
+        <f>P24*N24</f>
+        <v>361.85999999999996</v>
+      </c>
+      <c r="R24" s="46"/>
+      <c r="S24" s="50"/>
+    </row>
+    <row r="25" spans="1:19" s="79" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="77"/>
+      <c r="B25" s="37">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L25" s="48">
+        <v>10</v>
+      </c>
+      <c r="M25" s="48">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="N25" s="48">
+        <v>10100</v>
+      </c>
+      <c r="O25" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P25" s="51">
+        <v>0.24079999999999999</v>
+      </c>
+      <c r="Q25" s="51">
+        <f t="shared" si="2"/>
+        <v>2432.08</v>
+      </c>
+      <c r="R25" s="49"/>
+      <c r="S25" s="51"/>
+    </row>
+    <row r="26" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="77"/>
+      <c r="B26" s="37">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="I26" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="K26" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L26" s="45">
+        <v>10</v>
+      </c>
+      <c r="M26" s="45">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="N26" s="45">
+        <v>10100</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P26" s="50">
+        <v>5.2699999999999997E-2</v>
+      </c>
+      <c r="Q26" s="50">
+        <f t="shared" si="2"/>
+        <v>532.27</v>
+      </c>
+      <c r="R26" s="46"/>
+      <c r="S26" s="50"/>
+    </row>
+    <row r="27" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="77"/>
+      <c r="B27" s="37">
+        <f>ROW(B27) - ROW($B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="K27" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L27" s="48">
+        <v>4</v>
+      </c>
+      <c r="M27" s="48">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="N27" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="O27" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="P27" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q27" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="R27" s="49"/>
+      <c r="S27" s="51"/>
+    </row>
+    <row r="28" spans="1:19" s="79" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="77"/>
+      <c r="B28" s="37">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="K28" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L28" s="45">
+        <v>1</v>
+      </c>
+      <c r="M28" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N28" s="45">
+        <v>1050</v>
+      </c>
+      <c r="O28" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P28" s="50">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="Q28" s="50">
+        <f t="shared" si="2"/>
+        <v>45.255000000000003</v>
+      </c>
+      <c r="R28" s="46"/>
+      <c r="S28" s="50"/>
+    </row>
+    <row r="29" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="77"/>
+      <c r="B29" s="37">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="I29" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="K29" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L29" s="48">
+        <v>1</v>
+      </c>
+      <c r="M29" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N29" s="48">
+        <v>1050</v>
+      </c>
+      <c r="O29" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" s="51">
+        <v>1.15E-2</v>
+      </c>
+      <c r="Q29" s="51">
+        <f t="shared" si="2"/>
+        <v>12.074999999999999</v>
+      </c>
+      <c r="R29" s="49"/>
+      <c r="S29" s="51"/>
+    </row>
+    <row r="30" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="77"/>
+      <c r="B30" s="37">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="I30" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="K30" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="L30" s="45">
+        <v>6</v>
+      </c>
+      <c r="M30" s="45">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="N30" s="45">
+        <v>6100</v>
+      </c>
+      <c r="O30" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P30" s="50">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q30" s="50">
+        <f t="shared" si="2"/>
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="R30" s="46"/>
+      <c r="S30" s="50"/>
+    </row>
+    <row r="31" spans="1:19" s="79" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="77"/>
+      <c r="B31" s="37">
+        <f>ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="K31" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="L31" s="48">
+        <v>3</v>
+      </c>
+      <c r="M31" s="48">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="N31" s="48">
+        <v>3100</v>
+      </c>
+      <c r="O31" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P31" s="51">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Q31" s="51">
+        <f t="shared" si="2"/>
+        <v>14.57</v>
+      </c>
+      <c r="R31" s="49"/>
+      <c r="S31" s="51"/>
+    </row>
+    <row r="32" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="77"/>
+      <c r="B32" s="37">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="K32" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="L32" s="45">
+        <v>3</v>
+      </c>
+      <c r="M32" s="45">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="N32" s="45">
+        <v>3050</v>
+      </c>
+      <c r="O32" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P32" s="50">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="Q32" s="50">
+        <f t="shared" si="2"/>
+        <v>17.995000000000001</v>
+      </c>
+      <c r="R32" s="46"/>
+      <c r="S32" s="50"/>
+    </row>
+    <row r="33" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="77"/>
+      <c r="B33" s="37">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="I33" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="K33" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="48">
+        <v>2</v>
+      </c>
+      <c r="M33" s="48">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="N33" s="48">
+        <v>2100</v>
+      </c>
+      <c r="O33" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P33" s="51">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q33" s="51">
+        <f t="shared" si="2"/>
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="R33" s="49"/>
+      <c r="S33" s="51"/>
+    </row>
+    <row r="34" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="77"/>
+      <c r="B34" s="37">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="H34" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J34" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="K34" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="L34" s="45">
+        <v>1</v>
+      </c>
+      <c r="M34" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N34" s="45">
+        <v>1100</v>
+      </c>
+      <c r="O34" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P34" s="50">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" si="2"/>
+        <v>1.21</v>
+      </c>
+      <c r="R34" s="46"/>
+      <c r="S34" s="50"/>
+    </row>
+    <row r="35" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="77"/>
+      <c r="B35" s="37">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="L35" s="48">
+        <v>1</v>
+      </c>
+      <c r="M35" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N35" s="48">
+        <v>1100</v>
+      </c>
+      <c r="O35" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P35" s="51">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q35" s="51">
+        <f t="shared" si="2"/>
+        <v>0.44</v>
+      </c>
+      <c r="R35" s="49"/>
+      <c r="S35" s="51"/>
+    </row>
+    <row r="36" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="77"/>
+      <c r="B36" s="37">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="I36" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J36" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="K36" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="L36" s="45">
+        <v>10</v>
+      </c>
+      <c r="M36" s="45">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="N36" s="45">
+        <v>10100</v>
+      </c>
+      <c r="O36" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P36" s="50">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q36" s="50">
+        <f t="shared" si="2"/>
+        <v>4.04</v>
+      </c>
+      <c r="R36" s="46"/>
+      <c r="S36" s="50"/>
+    </row>
+    <row r="37" spans="1:19" s="79" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="77"/>
+      <c r="B37" s="37">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J37" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="K37" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L37" s="48">
+        <v>1</v>
+      </c>
+      <c r="M37" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N37" s="48">
+        <v>1080</v>
+      </c>
+      <c r="O37" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P37" s="51">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="Q37" s="51">
+        <f t="shared" si="2"/>
+        <v>13.176</v>
+      </c>
+      <c r="R37" s="49"/>
+      <c r="S37" s="51"/>
+    </row>
+    <row r="38" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="77"/>
+      <c r="B38" s="37">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J38" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="K38" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L38" s="45">
+        <v>1</v>
+      </c>
+      <c r="M38" s="45">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N38" s="45">
+        <v>1020</v>
+      </c>
+      <c r="O38" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P38" s="50">
+        <v>3.2805</v>
+      </c>
+      <c r="Q38" s="50">
+        <f t="shared" si="2"/>
+        <v>3346.11</v>
+      </c>
+      <c r="R38" s="46"/>
+      <c r="S38" s="50"/>
+    </row>
+    <row r="39" spans="1:19" s="79" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="77"/>
+      <c r="B39" s="37">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="H39" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J39" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="K39" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L39" s="48">
+        <v>1</v>
+      </c>
+      <c r="M39" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N39" s="48">
+        <v>1020</v>
+      </c>
+      <c r="O39" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P39" s="51">
+        <v>0.49009999999999998</v>
+      </c>
+      <c r="Q39" s="51">
+        <f t="shared" si="2"/>
+        <v>499.90199999999999</v>
+      </c>
+      <c r="R39" s="49"/>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="77"/>
+      <c r="B40" s="37">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="I40" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J40" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="K40" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L40" s="45">
+        <v>10</v>
+      </c>
+      <c r="M40" s="45">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="N40" s="45">
+        <v>10050</v>
+      </c>
+      <c r="O40" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P40" s="50">
+        <v>8.2900000000000001E-2</v>
+      </c>
+      <c r="Q40" s="50">
+        <f t="shared" si="2"/>
+        <v>833.14499999999998</v>
+      </c>
+      <c r="R40" s="46"/>
+      <c r="S40" s="50"/>
+    </row>
+    <row r="41" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="77"/>
+      <c r="B41" s="37">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="F41" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="I41" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="J41" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="K41" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L41" s="48">
+        <v>1</v>
+      </c>
+      <c r="M41" s="48">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N41" s="48">
+        <v>1020</v>
+      </c>
+      <c r="O41" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="P41" s="51">
+        <v>0.2414</v>
+      </c>
+      <c r="Q41" s="51">
+        <f t="shared" si="2"/>
+        <v>246.22800000000001</v>
+      </c>
+      <c r="R41" s="49"/>
+      <c r="S41" s="51"/>
+    </row>
+    <row r="42" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="77"/>
+      <c r="B42" s="37">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="I42" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J42" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="K42" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L42" s="45">
+        <v>2</v>
+      </c>
+      <c r="M42" s="45">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="N42" s="45">
+        <v>20100</v>
+      </c>
+      <c r="O42" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="P42" s="50">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="Q42" s="50">
+        <f t="shared" si="2"/>
+        <v>972.83999999999992</v>
+      </c>
+      <c r="R42" s="46"/>
+      <c r="S42" s="50"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="89" t="s">
+        <v>225</v>
+      </c>
+      <c r="O43" s="90"/>
+      <c r="P43" s="90"/>
+      <c r="Q43" s="68">
+        <f>SUM(Q10:Q42)</f>
+        <v>9769.2039999999997</v>
+      </c>
+      <c r="R43" s="85"/>
+      <c r="S43" s="86"/>
+    </row>
+    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="89" t="s">
+        <v>226</v>
+      </c>
+      <c r="O44" s="90"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="69">
+        <f>Q43/1000</f>
+        <v>9.7692040000000002</v>
+      </c>
+      <c r="R44" s="87"/>
+      <c r="S44" s="88"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S44"/>
+    <mergeCell ref="N44:P44"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1" xr:uid="{627FB971-793D-4AEF-B47A-C8F9085B4255}"/>
+    <hyperlink ref="O12" r:id="rId2" xr:uid="{CD51F70F-FC04-4BF0-87AF-4C9A8DF950CB}"/>
+    <hyperlink ref="O13" r:id="rId3" xr:uid="{029C345F-A39F-42BE-9D6C-82DC166C9326}"/>
+    <hyperlink ref="O14" r:id="rId4" xr:uid="{929FBB15-8077-481E-8177-1F51DC2C88B9}"/>
+    <hyperlink ref="O16" r:id="rId5" xr:uid="{28E1D816-3B09-4FA3-A003-B3F4BDA95F16}"/>
+    <hyperlink ref="O20" r:id="rId6" xr:uid="{BDF8F6EF-26F3-4986-9151-496CC9C1CB3D}"/>
+    <hyperlink ref="O22" r:id="rId7" xr:uid="{40A02C32-5998-4AE6-AE90-3B1499FAC42F}"/>
+    <hyperlink ref="O26" r:id="rId8" xr:uid="{E7E519B9-2C2E-43C0-A3DC-9C1B292187FA}"/>
+    <hyperlink ref="O28" r:id="rId9" xr:uid="{4FC9A57E-AD12-46C2-8B16-410D46B04C70}"/>
+    <hyperlink ref="O29" r:id="rId10" xr:uid="{D3FEDD23-56FF-4B5A-9611-7A5283D26C34}"/>
+    <hyperlink ref="O31" r:id="rId11" xr:uid="{3CBD983C-8888-4B15-A11D-09409E719A82}"/>
+    <hyperlink ref="O32" r:id="rId12" xr:uid="{BF12F8F7-9953-4F71-AAB2-3199A66537A2}"/>
+    <hyperlink ref="O33" r:id="rId13" xr:uid="{77D1771E-1D79-4611-86A4-6777949D1505}"/>
+    <hyperlink ref="O34" r:id="rId14" xr:uid="{533CE1F3-C431-460F-87AF-4D119C9D3B0E}"/>
+    <hyperlink ref="O35" r:id="rId15" xr:uid="{6CDA8F3A-56E7-4D3E-BAB4-2E12B2F2979A}"/>
+    <hyperlink ref="O36" r:id="rId16" xr:uid="{4F366CF4-9ECF-45B4-B69D-894A9EF0DFAF}"/>
+    <hyperlink ref="O37" r:id="rId17" xr:uid="{9F05DD87-3575-4F53-9DB7-25856276ED50}"/>
+    <hyperlink ref="O38" r:id="rId18" xr:uid="{32A6BD7D-C270-4A34-8B93-3F6C43507B6D}"/>
+    <hyperlink ref="O39" r:id="rId19" xr:uid="{1687D941-3C59-4F89-B4A7-0DE74F1FC459}"/>
+    <hyperlink ref="O40" r:id="rId20" xr:uid="{2E9A6BFF-C14A-46A4-BDB2-06267D7A9417}"/>
+    <hyperlink ref="O41" r:id="rId21" xr:uid="{91351711-C2B1-49E4-8874-294C8B9F1D3D}"/>
+    <hyperlink ref="O42" r:id="rId22" xr:uid="{E90C19F5-0A1E-4055-9D86-F4A75F07333D}"/>
+    <hyperlink ref="O25" r:id="rId23" xr:uid="{A9CE32FA-D5A3-4588-B571-9CE30C0C3F55}"/>
+    <hyperlink ref="O19" r:id="rId24" xr:uid="{039EB6C6-FF9A-4A7F-8D30-4A60683F606F}"/>
+    <hyperlink ref="O17" r:id="rId25" xr:uid="{7C1D5C80-C028-4564-A760-6D67C3E96266}"/>
+    <hyperlink ref="O18" r:id="rId26" xr:uid="{A669E1B2-8A6D-45B8-B333-ECF6AF131A7D}"/>
+    <hyperlink ref="O21" r:id="rId27" xr:uid="{01E8F6FD-1CA5-4EE5-B51E-73F144886C0A}"/>
+    <hyperlink ref="O23" r:id="rId28" xr:uid="{8B3DEC00-3F2F-4F60-8E68-19574A492D9E}"/>
+    <hyperlink ref="O24" r:id="rId29" xr:uid="{C9352AAE-8A6D-49D9-93A9-49B079080BF8}"/>
+    <hyperlink ref="O30" r:id="rId30" xr:uid="{13FA5982-39ED-422C-A048-6E6582BA3D43}"/>
+    <hyperlink ref="O11" r:id="rId31" xr:uid="{B1B56BA5-9A0B-4338-85D3-01648252D978}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId32"/>
+</worksheet>
 </file>